--- a/research/traditional_assets/database/data/pakistan/pakistan_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_software_system_application.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2548067524772778</v>
+        <v>0.2540997628950937</v>
       </c>
       <c r="C2">
-        <v>56.55871966461653</v>
+        <v>56.1222734669188</v>
       </c>
       <c r="D2">
-        <v>38.25871966461654</v>
+        <v>38.3885734669188</v>
       </c>
       <c r="E2">
-        <v>-5.73</v>
+        <v>-5.1637</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5662999999999999</v>
       </c>
       <c r="G2">
         <v>18.3</v>
@@ -1451,28 +1451,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02848489</v>
       </c>
       <c r="N2">
-        <v>4.484999999999999</v>
+        <v>4.45651511</v>
       </c>
       <c r="O2">
-        <v>1.30065</v>
+        <v>1.2923893819</v>
       </c>
       <c r="P2">
-        <v>3.18435</v>
+        <v>3.1641257281</v>
       </c>
       <c r="Q2">
-        <v>4.12435</v>
+        <v>4.1041257281</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2548067524772778</v>
+        <v>0.2563056897930239</v>
       </c>
       <c r="T2">
-        <v>1.278259280003682</v>
+        <v>1.287426594031991</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>157.451898181808</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2540997628950937</v>
+        <v>0.2533927733129096</v>
       </c>
       <c r="C3">
-        <v>56.1222734669188</v>
+        <v>55.68671174399317</v>
       </c>
       <c r="D3">
-        <v>38.3885734669188</v>
+        <v>38.51931174399316</v>
       </c>
       <c r="E3">
-        <v>-5.1637</v>
+        <v>-4.5974</v>
       </c>
       <c r="F3">
-        <v>0.5662999999999999</v>
+        <v>1.1326</v>
       </c>
       <c r="G3">
         <v>18.3</v>
@@ -1533,28 +1533,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M3">
-        <v>0.02848489</v>
+        <v>0.05696977999999999</v>
       </c>
       <c r="N3">
-        <v>4.45651511</v>
+        <v>4.428030219999999</v>
       </c>
       <c r="O3">
-        <v>1.2923893819</v>
+        <v>1.2841287638</v>
       </c>
       <c r="P3">
-        <v>3.1641257281</v>
+        <v>3.1439014562</v>
       </c>
       <c r="Q3">
-        <v>4.1041257281</v>
+        <v>4.0839014562</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2563056897930239</v>
+        <v>0.2578352176662343</v>
       </c>
       <c r="T3">
-        <v>1.287426594031991</v>
+        <v>1.296780996101695</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>157.451898181808</v>
+        <v>78.72594909090398</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2533927733129096</v>
+        <v>0.2526857837307255</v>
       </c>
       <c r="C4">
-        <v>55.68671174399317</v>
+        <v>55.2520435633711</v>
       </c>
       <c r="D4">
-        <v>38.51931174399316</v>
+        <v>38.65094356337109</v>
       </c>
       <c r="E4">
-        <v>-4.5974</v>
+        <v>-4.0311</v>
       </c>
       <c r="F4">
-        <v>1.1326</v>
+        <v>1.6989</v>
       </c>
       <c r="G4">
         <v>18.3</v>
@@ -1615,28 +1615,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M4">
-        <v>0.05696977999999999</v>
+        <v>0.08545466999999998</v>
       </c>
       <c r="N4">
-        <v>4.428030219999999</v>
+        <v>4.39954533</v>
       </c>
       <c r="O4">
-        <v>1.2841287638</v>
+        <v>1.2758681457</v>
       </c>
       <c r="P4">
-        <v>3.1439014562</v>
+        <v>3.1236771843</v>
       </c>
       <c r="Q4">
-        <v>4.0839014562</v>
+        <v>4.063677184299999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2578352176662343</v>
+        <v>0.2593962821966242</v>
       </c>
       <c r="T4">
-        <v>1.296780996101695</v>
+        <v>1.306328272440876</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>78.72594909090398</v>
+        <v>52.48396606060266</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2526857837307255</v>
+        <v>0.2519787941485414</v>
       </c>
       <c r="C5">
-        <v>55.2520435633711</v>
+        <v>54.81827811695474</v>
       </c>
       <c r="D5">
-        <v>38.65094356337109</v>
+        <v>38.78347811695474</v>
       </c>
       <c r="E5">
-        <v>-4.0311</v>
+        <v>-3.464800000000001</v>
       </c>
       <c r="F5">
-        <v>1.6989</v>
+        <v>2.2652</v>
       </c>
       <c r="G5">
         <v>18.3</v>
@@ -1697,28 +1697,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M5">
-        <v>0.08545466999999998</v>
+        <v>0.11393956</v>
       </c>
       <c r="N5">
-        <v>4.39954533</v>
+        <v>4.371060439999999</v>
       </c>
       <c r="O5">
-        <v>1.2758681457</v>
+        <v>1.2676075276</v>
       </c>
       <c r="P5">
-        <v>3.1236771843</v>
+        <v>3.103452912399999</v>
       </c>
       <c r="Q5">
-        <v>4.063677184299999</v>
+        <v>4.043452912399999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2593962821966242</v>
+        <v>0.2609898689047306</v>
       </c>
       <c r="T5">
-        <v>1.306328272440876</v>
+        <v>1.316074450370457</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>52.48396606060266</v>
+        <v>39.36297454545199</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2519787941485414</v>
+        <v>0.2512718045663572</v>
       </c>
       <c r="C6">
-        <v>54.81827811695474</v>
+        <v>54.3854247231566</v>
       </c>
       <c r="D6">
-        <v>38.78347811695474</v>
+        <v>38.9169247231566</v>
       </c>
       <c r="E6">
-        <v>-3.464800000000001</v>
+        <v>-2.8985</v>
       </c>
       <c r="F6">
-        <v>2.2652</v>
+        <v>2.8315</v>
       </c>
       <c r="G6">
         <v>18.3</v>
@@ -1779,28 +1779,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M6">
-        <v>0.11393956</v>
+        <v>0.14242445</v>
       </c>
       <c r="N6">
-        <v>4.371060439999999</v>
+        <v>4.342575549999999</v>
       </c>
       <c r="O6">
-        <v>1.2676075276</v>
+        <v>1.2593469095</v>
       </c>
       <c r="P6">
-        <v>3.103452912399999</v>
+        <v>3.0832286405</v>
       </c>
       <c r="Q6">
-        <v>4.043452912399999</v>
+        <v>4.023228640499999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2609898689047306</v>
+        <v>0.2626170048066918</v>
       </c>
       <c r="T6">
-        <v>1.316074450370457</v>
+        <v>1.326025810993293</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.36297454545199</v>
+        <v>31.49037963636159</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2512718045663572</v>
+        <v>0.2505648149841731</v>
       </c>
       <c r="C7">
-        <v>54.3854247231566</v>
+        <v>53.9534928290836</v>
       </c>
       <c r="D7">
-        <v>38.9169247231566</v>
+        <v>39.0512928290836</v>
       </c>
       <c r="E7">
-        <v>-2.8985</v>
+        <v>-2.3322</v>
       </c>
       <c r="F7">
-        <v>2.8315</v>
+        <v>3.3978</v>
       </c>
       <c r="G7">
         <v>18.3</v>
@@ -1861,28 +1861,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M7">
-        <v>0.14242445</v>
+        <v>0.17090934</v>
       </c>
       <c r="N7">
-        <v>4.342575549999999</v>
+        <v>4.31409066</v>
       </c>
       <c r="O7">
-        <v>1.2593469095</v>
+        <v>1.2510862914</v>
       </c>
       <c r="P7">
-        <v>3.0832286405</v>
+        <v>3.0630043686</v>
       </c>
       <c r="Q7">
-        <v>4.023228640499999</v>
+        <v>4.003004368599999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2626170048066918</v>
+        <v>0.2642787606214608</v>
       </c>
       <c r="T7">
-        <v>1.326025810993293</v>
+        <v>1.33618890269321</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.49037963636159</v>
+        <v>26.24198303030133</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2505648149841731</v>
+        <v>0.2498578254019891</v>
       </c>
       <c r="C8">
-        <v>53.95349282908361</v>
+        <v>53.52249201276642</v>
       </c>
       <c r="D8">
-        <v>39.0512928290836</v>
+        <v>39.18659201276642</v>
       </c>
       <c r="E8">
-        <v>-2.332200000000001</v>
+        <v>-1.765900000000001</v>
       </c>
       <c r="F8">
-        <v>3.3978</v>
+        <v>3.964099999999999</v>
       </c>
       <c r="G8">
         <v>18.3</v>
@@ -1943,28 +1943,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M8">
-        <v>0.17090934</v>
+        <v>0.19939423</v>
       </c>
       <c r="N8">
-        <v>4.31409066</v>
+        <v>4.285605769999999</v>
       </c>
       <c r="O8">
-        <v>1.2510862914</v>
+        <v>1.2428256733</v>
       </c>
       <c r="P8">
-        <v>3.0630043686</v>
+        <v>3.0427800967</v>
       </c>
       <c r="Q8">
-        <v>4.003004368599999</v>
+        <v>3.9827800967</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2642787606214608</v>
+        <v>0.2659762531204183</v>
       </c>
       <c r="T8">
-        <v>1.33618890269321</v>
+        <v>1.346570555504954</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.24198303030133</v>
+        <v>22.49312831168685</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.249857825401989</v>
+        <v>0.2491508358198049</v>
       </c>
       <c r="C9">
-        <v>53.52249201276642</v>
+        <v>53.0924319854355</v>
       </c>
       <c r="D9">
-        <v>39.18659201276643</v>
+        <v>39.3228319854355</v>
       </c>
       <c r="E9">
-        <v>-1.7659</v>
+        <v>-1.199600000000001</v>
       </c>
       <c r="F9">
-        <v>3.9641</v>
+        <v>4.530399999999999</v>
       </c>
       <c r="G9">
         <v>18.3</v>
@@ -2025,28 +2025,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M9">
-        <v>0.19939423</v>
+        <v>0.22787912</v>
       </c>
       <c r="N9">
-        <v>4.285605769999999</v>
+        <v>4.25712088</v>
       </c>
       <c r="O9">
-        <v>1.2428256733</v>
+        <v>1.2345650552</v>
       </c>
       <c r="P9">
-        <v>3.0427800967</v>
+        <v>3.0225558248</v>
       </c>
       <c r="Q9">
-        <v>3.9827800967</v>
+        <v>3.962555824799999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2659762531204183</v>
+        <v>0.2677106476302227</v>
       </c>
       <c r="T9">
-        <v>1.346570555504954</v>
+        <v>1.3571778964213</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.49312831168685</v>
+        <v>19.681487272726</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2491508358198049</v>
+        <v>0.2484438462376208</v>
       </c>
       <c r="C10">
-        <v>53.0924319854355</v>
+        <v>52.66332259384451</v>
       </c>
       <c r="D10">
-        <v>39.3228319854355</v>
+        <v>39.46002259384451</v>
       </c>
       <c r="E10">
-        <v>-1.199600000000001</v>
+        <v>-0.6333000000000011</v>
       </c>
       <c r="F10">
-        <v>4.530399999999999</v>
+        <v>5.096699999999999</v>
       </c>
       <c r="G10">
         <v>18.3</v>
@@ -2107,28 +2107,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M10">
-        <v>0.22787912</v>
+        <v>0.25636401</v>
       </c>
       <c r="N10">
-        <v>4.25712088</v>
+        <v>4.228635989999999</v>
       </c>
       <c r="O10">
-        <v>1.2345650552</v>
+        <v>1.2263044371</v>
       </c>
       <c r="P10">
-        <v>3.0225558248</v>
+        <v>3.002331552899999</v>
       </c>
       <c r="Q10">
-        <v>3.962555824799999</v>
+        <v>3.942331552899999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2677106476302227</v>
+        <v>0.2694831607006822</v>
       </c>
       <c r="T10">
-        <v>1.3571778964213</v>
+        <v>1.368018365709435</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.681487272726</v>
+        <v>17.49465535353422</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2484438462376208</v>
+        <v>0.2477368566554367</v>
       </c>
       <c r="C11">
-        <v>52.66332259384451</v>
+        <v>52.23517382264272</v>
       </c>
       <c r="D11">
-        <v>39.46002259384451</v>
+        <v>39.59817382264272</v>
       </c>
       <c r="E11">
-        <v>-0.6333000000000011</v>
+        <v>-0.06700000000000106</v>
       </c>
       <c r="F11">
-        <v>5.096699999999999</v>
+        <v>5.662999999999999</v>
       </c>
       <c r="G11">
         <v>18.3</v>
@@ -2189,28 +2189,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M11">
-        <v>0.25636401</v>
+        <v>0.2848489</v>
       </c>
       <c r="N11">
-        <v>4.228635989999999</v>
+        <v>4.200151099999999</v>
       </c>
       <c r="O11">
-        <v>1.2263044371</v>
+        <v>1.218043819</v>
       </c>
       <c r="P11">
-        <v>3.002331552899999</v>
+        <v>2.982107280999999</v>
       </c>
       <c r="Q11">
-        <v>3.942331552899999</v>
+        <v>3.922107280999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2694831607006822</v>
+        <v>0.2712950629504852</v>
       </c>
       <c r="T11">
-        <v>1.368018365709435</v>
+        <v>1.379099734315083</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.49465535353422</v>
+        <v>15.7451898181808</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2477368566554367</v>
+        <v>0.2470298670732526</v>
       </c>
       <c r="C12">
-        <v>52.23517382264272</v>
+        <v>51.80799579679744</v>
       </c>
       <c r="D12">
-        <v>39.59817382264272</v>
+        <v>39.73729579679743</v>
       </c>
       <c r="E12">
-        <v>-0.06700000000000017</v>
+        <v>0.499299999999999</v>
       </c>
       <c r="F12">
-        <v>5.663</v>
+        <v>6.229299999999999</v>
       </c>
       <c r="G12">
         <v>18.3</v>
@@ -2271,28 +2271,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M12">
-        <v>0.2848489</v>
+        <v>0.3133337899999999</v>
       </c>
       <c r="N12">
-        <v>4.200151099999999</v>
+        <v>4.17166621</v>
       </c>
       <c r="O12">
-        <v>1.218043819</v>
+        <v>1.2097832009</v>
       </c>
       <c r="P12">
-        <v>2.982107280999999</v>
+        <v>2.9618830091</v>
       </c>
       <c r="Q12">
-        <v>3.922107280999999</v>
+        <v>3.9018830091</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2712950629504852</v>
+        <v>0.2731476821047782</v>
       </c>
       <c r="T12">
-        <v>1.379099734315083</v>
+        <v>1.39043012243996</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.74518981818079</v>
+        <v>14.31380892561891</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2470298670732526</v>
+        <v>0.2463228774910685</v>
       </c>
       <c r="C13">
-        <v>51.80799579679744</v>
+        <v>51.38179878406759</v>
       </c>
       <c r="D13">
-        <v>39.73729579679743</v>
+        <v>39.87739878406759</v>
       </c>
       <c r="E13">
-        <v>0.499299999999999</v>
+        <v>1.065599999999999</v>
       </c>
       <c r="F13">
-        <v>6.229299999999999</v>
+        <v>6.795599999999999</v>
       </c>
       <c r="G13">
         <v>18.3</v>
@@ -2353,28 +2353,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M13">
-        <v>0.3133337899999999</v>
+        <v>0.3418186799999999</v>
       </c>
       <c r="N13">
-        <v>4.17166621</v>
+        <v>4.143181319999999</v>
       </c>
       <c r="O13">
-        <v>1.2097832009</v>
+        <v>1.2015225828</v>
       </c>
       <c r="P13">
-        <v>2.9618830091</v>
+        <v>2.9416587372</v>
       </c>
       <c r="Q13">
-        <v>3.9018830091</v>
+        <v>3.8816587372</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2731476821047782</v>
+        <v>0.2750424062398505</v>
       </c>
       <c r="T13">
-        <v>1.39043012243996</v>
+        <v>1.402018019385856</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.31380892561891</v>
+        <v>13.12099151515066</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2463228774910685</v>
+        <v>0.2457543379088844</v>
       </c>
       <c r="C14">
-        <v>51.38179878406759</v>
+        <v>50.92888406933013</v>
       </c>
       <c r="D14">
-        <v>39.87739878406759</v>
+        <v>39.99078406933013</v>
       </c>
       <c r="E14">
-        <v>1.065599999999999</v>
+        <v>1.631899999999999</v>
       </c>
       <c r="F14">
-        <v>6.795599999999999</v>
+        <v>7.361899999999999</v>
       </c>
       <c r="G14">
         <v>18.3</v>
@@ -2435,45 +2435,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M14">
-        <v>0.3418186799999999</v>
+        <v>0.38134642</v>
       </c>
       <c r="N14">
-        <v>4.143181319999999</v>
+        <v>4.10365358</v>
       </c>
       <c r="O14">
-        <v>1.2015225828</v>
+        <v>1.1900595382</v>
       </c>
       <c r="P14">
-        <v>2.9416587372</v>
+        <v>2.9135940418</v>
       </c>
       <c r="Q14">
-        <v>3.8816587372</v>
+        <v>3.8535940418</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2750424062398505</v>
+        <v>0.2769806872515913</v>
       </c>
       <c r="T14">
-        <v>1.402018019385856</v>
+        <v>1.413872304767291</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.29</v>
       </c>
       <c r="W14">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.12099151515066</v>
+        <v>11.76096002159926</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2457543379088844</v>
+        <v>0.2450579983267003</v>
       </c>
       <c r="C15">
-        <v>50.92888406933013</v>
+        <v>50.5023383883733</v>
       </c>
       <c r="D15">
-        <v>39.99078406933013</v>
+        <v>40.1305383883733</v>
       </c>
       <c r="E15">
-        <v>1.631899999999999</v>
+        <v>2.1982</v>
       </c>
       <c r="F15">
-        <v>7.361899999999999</v>
+        <v>7.9282</v>
       </c>
       <c r="G15">
         <v>18.3</v>
@@ -2517,28 +2517,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M15">
-        <v>0.38134642</v>
+        <v>0.41068076</v>
       </c>
       <c r="N15">
-        <v>4.10365358</v>
+        <v>4.074319239999999</v>
       </c>
       <c r="O15">
-        <v>1.1900595382</v>
+        <v>1.1815525796</v>
       </c>
       <c r="P15">
-        <v>2.9135940418</v>
+        <v>2.8927666604</v>
       </c>
       <c r="Q15">
-        <v>3.8535940418</v>
+        <v>3.832766660399999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2769806872515913</v>
+        <v>0.2789640445659306</v>
       </c>
       <c r="T15">
-        <v>1.413872304767291</v>
+        <v>1.426002271204107</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.76096002159926</v>
+        <v>10.92089144862788</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2450579983267003</v>
+        <v>0.2443616587445162</v>
       </c>
       <c r="C16">
-        <v>50.5023383883733</v>
+        <v>50.07677292146933</v>
       </c>
       <c r="D16">
-        <v>40.1305383883733</v>
+        <v>40.27127292146933</v>
       </c>
       <c r="E16">
-        <v>2.1982</v>
+        <v>2.7645</v>
       </c>
       <c r="F16">
-        <v>7.9282</v>
+        <v>8.4945</v>
       </c>
       <c r="G16">
         <v>18.3</v>
@@ -2599,28 +2599,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M16">
-        <v>0.41068076</v>
+        <v>0.4400151</v>
       </c>
       <c r="N16">
-        <v>4.074319239999999</v>
+        <v>4.044984899999999</v>
       </c>
       <c r="O16">
-        <v>1.1815525796</v>
+        <v>1.173045621</v>
       </c>
       <c r="P16">
-        <v>2.8927666604</v>
+        <v>2.871939278999999</v>
       </c>
       <c r="Q16">
-        <v>3.832766660399999</v>
+        <v>3.811939278999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2789640445659306</v>
+        <v>0.2809940691111955</v>
       </c>
       <c r="T16">
-        <v>1.426002271204107</v>
+        <v>1.438417648615908</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.92089144862788</v>
+        <v>10.19283201871936</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2443616587445162</v>
+        <v>0.2438584391623321</v>
       </c>
       <c r="C17">
-        <v>50.07677292146933</v>
+        <v>49.6127926873893</v>
       </c>
       <c r="D17">
-        <v>40.27127292146933</v>
+        <v>40.3735926873893</v>
       </c>
       <c r="E17">
-        <v>2.764499999999998</v>
+        <v>3.330799999999998</v>
       </c>
       <c r="F17">
-        <v>8.494499999999999</v>
+        <v>9.060799999999999</v>
       </c>
       <c r="G17">
         <v>18.3</v>
@@ -2681,45 +2681,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M17">
-        <v>0.4400150999999999</v>
+        <v>0.4847527999999999</v>
       </c>
       <c r="N17">
-        <v>4.044984899999999</v>
+        <v>4.0002472</v>
       </c>
       <c r="O17">
-        <v>1.173045621</v>
+        <v>1.160071688</v>
       </c>
       <c r="P17">
-        <v>2.871939278999999</v>
+        <v>2.840175512</v>
       </c>
       <c r="Q17">
-        <v>3.811939278999999</v>
+        <v>3.780175512</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2809940691111955</v>
+        <v>0.2830724275742049</v>
       </c>
       <c r="T17">
-        <v>1.438417648615908</v>
+        <v>1.451128630251799</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.29</v>
       </c>
       <c r="W17">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.19283201871936</v>
+        <v>9.252138409515117</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2438584391623321</v>
+        <v>0.243174169580148</v>
       </c>
       <c r="C18">
-        <v>49.6127926873893</v>
+        <v>49.18646247907094</v>
       </c>
       <c r="D18">
-        <v>40.3735926873893</v>
+        <v>40.51356247907093</v>
       </c>
       <c r="E18">
-        <v>3.330799999999998</v>
+        <v>3.8971</v>
       </c>
       <c r="F18">
-        <v>9.060799999999999</v>
+        <v>9.6271</v>
       </c>
       <c r="G18">
         <v>18.3</v>
@@ -2763,28 +2763,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M18">
-        <v>0.4847527999999999</v>
+        <v>0.51504985</v>
       </c>
       <c r="N18">
-        <v>4.0002472</v>
+        <v>3.969950149999999</v>
       </c>
       <c r="O18">
-        <v>1.160071688</v>
+        <v>1.1512855435</v>
       </c>
       <c r="P18">
-        <v>2.840175512</v>
+        <v>2.8186646065</v>
       </c>
       <c r="Q18">
-        <v>3.780175512</v>
+        <v>3.7586646065</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2830724275742049</v>
+        <v>0.2852008669640337</v>
       </c>
       <c r="T18">
-        <v>1.451128630251799</v>
+        <v>1.464145900601808</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.252138409515117</v>
+        <v>8.707894973661286</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.243174169580148</v>
+        <v>0.2424898999979638</v>
       </c>
       <c r="C19">
-        <v>49.18646247907094</v>
+        <v>48.76110615981221</v>
       </c>
       <c r="D19">
-        <v>40.51356247907093</v>
+        <v>40.65450615981221</v>
       </c>
       <c r="E19">
-        <v>3.8971</v>
+        <v>4.4634</v>
       </c>
       <c r="F19">
-        <v>9.6271</v>
+        <v>10.1934</v>
       </c>
       <c r="G19">
         <v>18.3</v>
@@ -2845,28 +2845,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M19">
-        <v>0.51504985</v>
+        <v>0.5453469</v>
       </c>
       <c r="N19">
-        <v>3.969950149999999</v>
+        <v>3.939653099999999</v>
       </c>
       <c r="O19">
-        <v>1.1512855435</v>
+        <v>1.142499399</v>
       </c>
       <c r="P19">
-        <v>2.8186646065</v>
+        <v>2.797153701</v>
       </c>
       <c r="Q19">
-        <v>3.7586646065</v>
+        <v>3.737153701</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2852008669640337</v>
+        <v>0.287381219509712</v>
       </c>
       <c r="T19">
-        <v>1.464145900601808</v>
+        <v>1.477480665350597</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.707894973661286</v>
+        <v>8.224123030680104</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2424898999979639</v>
+        <v>0.2418056304157798</v>
       </c>
       <c r="C20">
-        <v>48.7611061598122</v>
+        <v>48.33673392936079</v>
       </c>
       <c r="D20">
-        <v>40.6545061598122</v>
+        <v>40.79643392936078</v>
       </c>
       <c r="E20">
-        <v>4.463399999999998</v>
+        <v>5.029699999999998</v>
       </c>
       <c r="F20">
-        <v>10.1934</v>
+        <v>10.7597</v>
       </c>
       <c r="G20">
         <v>18.3</v>
@@ -2927,28 +2927,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M20">
-        <v>0.5453469</v>
+        <v>0.5756439499999999</v>
       </c>
       <c r="N20">
-        <v>3.939653099999999</v>
+        <v>3.90935605</v>
       </c>
       <c r="O20">
-        <v>1.142499399</v>
+        <v>1.1337132545</v>
       </c>
       <c r="P20">
-        <v>2.797153701</v>
+        <v>2.7756427955</v>
       </c>
       <c r="Q20">
-        <v>3.737153701</v>
+        <v>3.7156427955</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.287381219509712</v>
+        <v>0.2896154079207158</v>
       </c>
       <c r="T20">
-        <v>1.477480665350597</v>
+        <v>1.491144683549974</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.224123030680104</v>
+        <v>7.791274450117994</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2418056304157798</v>
+        <v>0.2412349608335957</v>
       </c>
       <c r="C21">
-        <v>48.33673392936079</v>
+        <v>47.8895594113409</v>
       </c>
       <c r="D21">
-        <v>40.79643392936078</v>
+        <v>40.91555941134091</v>
       </c>
       <c r="E21">
-        <v>5.029699999999998</v>
+        <v>5.596</v>
       </c>
       <c r="F21">
-        <v>10.7597</v>
+        <v>11.326</v>
       </c>
       <c r="G21">
         <v>18.3</v>
@@ -3009,45 +3009,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M21">
-        <v>0.5756439499999999</v>
+        <v>0.6150018</v>
       </c>
       <c r="N21">
-        <v>3.90935605</v>
+        <v>3.869998199999999</v>
       </c>
       <c r="O21">
-        <v>1.1337132545</v>
+        <v>1.122299478</v>
       </c>
       <c r="P21">
-        <v>2.7756427955</v>
+        <v>2.747698722</v>
       </c>
       <c r="Q21">
-        <v>3.7156427955</v>
+        <v>3.687698722</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2896154079207158</v>
+        <v>0.2919054510419946</v>
       </c>
       <c r="T21">
-        <v>1.491144683549974</v>
+        <v>1.505150302204335</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.29</v>
       </c>
       <c r="W21">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.791274450117994</v>
+        <v>7.292661582453904</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2412349608335957</v>
+        <v>0.2405563712514116</v>
       </c>
       <c r="C22">
-        <v>47.8895594113409</v>
+        <v>47.46582148613911</v>
       </c>
       <c r="D22">
-        <v>40.91555941134091</v>
+        <v>41.05812148613911</v>
       </c>
       <c r="E22">
-        <v>5.596</v>
+        <v>6.1623</v>
       </c>
       <c r="F22">
-        <v>11.326</v>
+        <v>11.8923</v>
       </c>
       <c r="G22">
         <v>18.3</v>
@@ -3091,28 +3091,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M22">
-        <v>0.6150018</v>
+        <v>0.64575189</v>
       </c>
       <c r="N22">
-        <v>3.869998199999999</v>
+        <v>3.839248109999999</v>
       </c>
       <c r="O22">
-        <v>1.122299478</v>
+        <v>1.1133819519</v>
       </c>
       <c r="P22">
-        <v>2.747698722</v>
+        <v>2.7258661581</v>
       </c>
       <c r="Q22">
-        <v>3.687698722</v>
+        <v>3.6658661581</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2919054510419946</v>
+        <v>0.2942534699384957</v>
       </c>
       <c r="T22">
-        <v>1.505150302204335</v>
+        <v>1.519510493482858</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.292661582453904</v>
+        <v>6.945391983289432</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2405563712514116</v>
+        <v>0.2398777816692275</v>
       </c>
       <c r="C23">
-        <v>47.46582148613911</v>
+        <v>47.04308049255867</v>
       </c>
       <c r="D23">
-        <v>41.05812148613911</v>
+        <v>41.20168049255866</v>
       </c>
       <c r="E23">
-        <v>6.162299999999998</v>
+        <v>6.728599999999998</v>
       </c>
       <c r="F23">
-        <v>11.8923</v>
+        <v>12.4586</v>
       </c>
       <c r="G23">
         <v>18.3</v>
@@ -3173,28 +3173,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M23">
-        <v>0.64575189</v>
+        <v>0.6765019799999999</v>
       </c>
       <c r="N23">
-        <v>3.839248109999999</v>
+        <v>3.80849802</v>
       </c>
       <c r="O23">
-        <v>1.1133819519</v>
+        <v>1.1044644258</v>
       </c>
       <c r="P23">
-        <v>2.7258661581</v>
+        <v>2.7040335942</v>
       </c>
       <c r="Q23">
-        <v>3.6658661581</v>
+        <v>3.6440335942</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2942534699384957</v>
+        <v>0.2966616944477275</v>
       </c>
       <c r="T23">
-        <v>1.519510493482858</v>
+        <v>1.534238894794163</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.945391983289432</v>
+        <v>6.629692347685368</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2398777816692275</v>
+        <v>0.2391991920870433</v>
       </c>
       <c r="C24">
-        <v>47.04308049255867</v>
+        <v>46.62134692455361</v>
       </c>
       <c r="D24">
-        <v>41.20168049255866</v>
+        <v>41.3462469245536</v>
       </c>
       <c r="E24">
-        <v>6.728599999999998</v>
+        <v>7.294899999999998</v>
       </c>
       <c r="F24">
-        <v>12.4586</v>
+        <v>13.0249</v>
       </c>
       <c r="G24">
         <v>18.3</v>
@@ -3255,28 +3255,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M24">
-        <v>0.6765019799999999</v>
+        <v>0.7072520699999999</v>
       </c>
       <c r="N24">
-        <v>3.80849802</v>
+        <v>3.777747929999999</v>
       </c>
       <c r="O24">
-        <v>1.1044644258</v>
+        <v>1.0955468997</v>
       </c>
       <c r="P24">
-        <v>2.7040335942</v>
+        <v>2.6822010303</v>
       </c>
       <c r="Q24">
-        <v>3.6440335942</v>
+        <v>3.6222010303</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2966616944477275</v>
+        <v>0.2991324702429135</v>
       </c>
       <c r="T24">
-        <v>1.534238894794163</v>
+        <v>1.549349851983683</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.629692347685368</v>
+        <v>6.341444854307744</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2391991920870433</v>
+        <v>0.2386910025048593</v>
       </c>
       <c r="C25">
-        <v>46.62134692455361</v>
+        <v>46.1639775209869</v>
       </c>
       <c r="D25">
-        <v>41.3462469245536</v>
+        <v>41.4551775209869</v>
       </c>
       <c r="E25">
-        <v>7.294899999999998</v>
+        <v>7.8612</v>
       </c>
       <c r="F25">
-        <v>13.0249</v>
+        <v>13.5912</v>
       </c>
       <c r="G25">
         <v>18.3</v>
@@ -3337,45 +3337,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M25">
-        <v>0.7072520699999999</v>
+        <v>0.7515933600000001</v>
       </c>
       <c r="N25">
-        <v>3.777747929999999</v>
+        <v>3.733406639999999</v>
       </c>
       <c r="O25">
-        <v>1.0955468997</v>
+        <v>1.0826879256</v>
       </c>
       <c r="P25">
-        <v>2.6822010303</v>
+        <v>2.6507187144</v>
       </c>
       <c r="Q25">
-        <v>3.6222010303</v>
+        <v>3.590718714399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2991324702429135</v>
+        <v>0.3016682664537622</v>
       </c>
       <c r="T25">
-        <v>1.549349851983683</v>
+        <v>1.564858465941349</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.29</v>
       </c>
       <c r="W25">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.341444854307744</v>
+        <v>5.967322542604686</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2386910025048593</v>
+        <v>0.2380195129226751</v>
       </c>
       <c r="C26">
-        <v>46.1639775209869</v>
+        <v>45.7424948676219</v>
       </c>
       <c r="D26">
-        <v>41.4551775209869</v>
+        <v>41.5999948676219</v>
       </c>
       <c r="E26">
-        <v>7.861199999999998</v>
+        <v>8.427499999999998</v>
       </c>
       <c r="F26">
-        <v>13.5912</v>
+        <v>14.1575</v>
       </c>
       <c r="G26">
         <v>18.3</v>
@@ -3419,28 +3419,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M26">
-        <v>0.75159336</v>
+        <v>0.78290975</v>
       </c>
       <c r="N26">
-        <v>3.733406639999999</v>
+        <v>3.702090249999999</v>
       </c>
       <c r="O26">
-        <v>1.0826879256</v>
+        <v>1.0736061725</v>
       </c>
       <c r="P26">
-        <v>2.6507187144</v>
+        <v>2.6284840775</v>
       </c>
       <c r="Q26">
-        <v>3.590718714399999</v>
+        <v>3.5684840775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.3016682664537622</v>
+        <v>0.3042716838969002</v>
       </c>
       <c r="T26">
-        <v>1.564858465941349</v>
+        <v>1.580780642937886</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.967322542604686</v>
+        <v>5.7286296409005</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2380195129226751</v>
+        <v>0.237348023340491</v>
       </c>
       <c r="C27">
-        <v>45.7424948676219</v>
+        <v>45.32202755587089</v>
       </c>
       <c r="D27">
-        <v>41.5999948676219</v>
+        <v>41.74582755587088</v>
       </c>
       <c r="E27">
-        <v>8.427499999999998</v>
+        <v>8.993799999999998</v>
       </c>
       <c r="F27">
-        <v>14.1575</v>
+        <v>14.7238</v>
       </c>
       <c r="G27">
         <v>18.3</v>
@@ -3501,28 +3501,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M27">
-        <v>0.78290975</v>
+        <v>0.8142261399999999</v>
       </c>
       <c r="N27">
-        <v>3.702090249999999</v>
+        <v>3.67077386</v>
       </c>
       <c r="O27">
-        <v>1.0736061725</v>
+        <v>1.0645244194</v>
       </c>
       <c r="P27">
-        <v>2.6284840775</v>
+        <v>2.6062494406</v>
       </c>
       <c r="Q27">
-        <v>3.5684840775</v>
+        <v>3.5462494406</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.3042716838969002</v>
+        <v>0.3069454639736365</v>
       </c>
       <c r="T27">
-        <v>1.580780642937886</v>
+        <v>1.597133149042438</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.7286296409005</v>
+        <v>5.508297731635096</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.237348023340491</v>
+        <v>0.2366765337583069</v>
       </c>
       <c r="C28">
-        <v>45.32202755587089</v>
+        <v>44.90258630142478</v>
       </c>
       <c r="D28">
-        <v>41.74582755587088</v>
+        <v>41.89268630142477</v>
       </c>
       <c r="E28">
-        <v>8.993799999999998</v>
+        <v>9.560099999999998</v>
       </c>
       <c r="F28">
-        <v>14.7238</v>
+        <v>15.2901</v>
       </c>
       <c r="G28">
         <v>18.3</v>
@@ -3583,28 +3583,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M28">
-        <v>0.8142261399999999</v>
+        <v>0.84554253</v>
       </c>
       <c r="N28">
-        <v>3.67077386</v>
+        <v>3.63945747</v>
       </c>
       <c r="O28">
-        <v>1.0645244194</v>
+        <v>1.0554426663</v>
       </c>
       <c r="P28">
-        <v>2.6062494406</v>
+        <v>2.5840148037</v>
       </c>
       <c r="Q28">
-        <v>3.5462494406</v>
+        <v>3.5240148037</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.3069454639736365</v>
+        <v>0.3096924982990506</v>
       </c>
       <c r="T28">
-        <v>1.597133149042438</v>
+        <v>1.613933669012868</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.508297731635096</v>
+        <v>5.304286704537499</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2366765337583069</v>
+        <v>0.2360050441761228</v>
       </c>
       <c r="C29">
-        <v>44.90258630142478</v>
+        <v>44.48418197129495</v>
       </c>
       <c r="D29">
-        <v>41.89268630142477</v>
+        <v>42.04058197129495</v>
       </c>
       <c r="E29">
-        <v>9.560099999999998</v>
+        <v>10.1264</v>
       </c>
       <c r="F29">
-        <v>15.2901</v>
+        <v>15.8564</v>
       </c>
       <c r="G29">
         <v>18.3</v>
@@ -3665,28 +3665,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M29">
-        <v>0.84554253</v>
+        <v>0.8768589200000001</v>
       </c>
       <c r="N29">
-        <v>3.63945747</v>
+        <v>3.608141079999999</v>
       </c>
       <c r="O29">
-        <v>1.0554426663</v>
+        <v>1.0463609132</v>
       </c>
       <c r="P29">
-        <v>2.5840148037</v>
+        <v>2.561780166799999</v>
       </c>
       <c r="Q29">
-        <v>3.5240148037</v>
+        <v>3.501780166799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.3096924982990506</v>
+        <v>0.3125158391335039</v>
       </c>
       <c r="T29">
-        <v>1.613933669012868</v>
+        <v>1.631200870093587</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.304286704537499</v>
+        <v>5.114847893661159</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2360050441761228</v>
+        <v>0.2353335545939388</v>
       </c>
       <c r="C30">
-        <v>44.48418197129495</v>
+        <v>44.06682558649364</v>
       </c>
       <c r="D30">
-        <v>42.04058197129495</v>
+        <v>42.18952558649364</v>
       </c>
       <c r="E30">
-        <v>10.1264</v>
+        <v>10.6927</v>
       </c>
       <c r="F30">
-        <v>15.8564</v>
+        <v>16.4227</v>
       </c>
       <c r="G30">
         <v>18.3</v>
@@ -3747,28 +3747,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M30">
-        <v>0.8768589200000001</v>
+        <v>0.90817531</v>
       </c>
       <c r="N30">
-        <v>3.608141079999999</v>
+        <v>3.57682469</v>
       </c>
       <c r="O30">
-        <v>1.0463609132</v>
+        <v>1.0372791601</v>
       </c>
       <c r="P30">
-        <v>2.561780166799999</v>
+        <v>2.5395455299</v>
       </c>
       <c r="Q30">
-        <v>3.501780166799999</v>
+        <v>3.4795455299</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.3125158391335039</v>
+        <v>0.3154187106956884</v>
       </c>
       <c r="T30">
-        <v>1.631200870093587</v>
+        <v>1.64895447120475</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.114847893661159</v>
+        <v>4.9384738283625</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2353335545939388</v>
+        <v>0.2346620650117546</v>
       </c>
       <c r="C31">
-        <v>44.06682558649364</v>
+        <v>43.65052832477176</v>
       </c>
       <c r="D31">
-        <v>42.18952558649364</v>
+        <v>42.33952832477176</v>
       </c>
       <c r="E31">
-        <v>10.6927</v>
+        <v>11.259</v>
       </c>
       <c r="F31">
-        <v>16.4227</v>
+        <v>16.989</v>
       </c>
       <c r="G31">
         <v>18.3</v>
@@ -3829,28 +3829,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M31">
-        <v>0.90817531</v>
+        <v>0.9394916999999999</v>
       </c>
       <c r="N31">
-        <v>3.57682469</v>
+        <v>3.545508299999999</v>
       </c>
       <c r="O31">
-        <v>1.0372791601</v>
+        <v>1.028197407</v>
       </c>
       <c r="P31">
-        <v>2.5395455299</v>
+        <v>2.517310892999999</v>
       </c>
       <c r="Q31">
-        <v>3.4795455299</v>
+        <v>3.457310892999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.3154187106956884</v>
+        <v>0.3184045214453637</v>
       </c>
       <c r="T31">
-        <v>1.64895447120475</v>
+        <v>1.667215318061945</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.9384738283625</v>
+        <v>4.77385803408375</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2346620650117546</v>
+        <v>0.2339905754295705</v>
       </c>
       <c r="C32">
-        <v>43.65052832477176</v>
+        <v>43.23530152341507</v>
       </c>
       <c r="D32">
-        <v>42.33952832477176</v>
+        <v>42.49060152341507</v>
       </c>
       <c r="E32">
-        <v>11.259</v>
+        <v>11.8253</v>
       </c>
       <c r="F32">
-        <v>16.989</v>
+        <v>17.5553</v>
       </c>
       <c r="G32">
         <v>18.3</v>
@@ -3911,28 +3911,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M32">
-        <v>0.9394916999999999</v>
+        <v>0.97080809</v>
       </c>
       <c r="N32">
-        <v>3.545508299999999</v>
+        <v>3.514191909999999</v>
       </c>
       <c r="O32">
-        <v>1.028197407</v>
+        <v>1.0191156539</v>
       </c>
       <c r="P32">
-        <v>2.517310892999999</v>
+        <v>2.4950762561</v>
       </c>
       <c r="Q32">
-        <v>3.457310892999999</v>
+        <v>3.435076256099999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.3184045214453637</v>
+        <v>0.3214768774341602</v>
       </c>
       <c r="T32">
-        <v>1.667215318061945</v>
+        <v>1.686005464828045</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.77385803408375</v>
+        <v>4.619862613629435</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2339905754295705</v>
+        <v>0.2338870858473864</v>
       </c>
       <c r="C33">
-        <v>43.23530152341507</v>
+        <v>42.69238077127039</v>
       </c>
       <c r="D33">
-        <v>42.49060152341507</v>
+        <v>42.51398077127039</v>
       </c>
       <c r="E33">
-        <v>11.8253</v>
+        <v>12.3916</v>
       </c>
       <c r="F33">
-        <v>17.5553</v>
+        <v>18.1216</v>
       </c>
       <c r="G33">
         <v>18.3</v>
@@ -3993,45 +3993,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M33">
-        <v>0.97080809</v>
+        <v>1.04742848</v>
       </c>
       <c r="N33">
-        <v>3.514191909999999</v>
+        <v>3.43757152</v>
       </c>
       <c r="O33">
-        <v>1.0191156539</v>
+        <v>0.9968957407999999</v>
       </c>
       <c r="P33">
-        <v>2.4950762561</v>
+        <v>2.4406757792</v>
       </c>
       <c r="Q33">
-        <v>3.435076256099999</v>
+        <v>3.3806757792</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3214768774341602</v>
+        <v>0.3246395968343918</v>
       </c>
       <c r="T33">
-        <v>1.686005464828045</v>
+        <v>1.705348262969618</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.29</v>
       </c>
       <c r="W33">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.619862613629435</v>
+        <v>4.281915267379401</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2338870858473864</v>
+        <v>0.2332333462652023</v>
       </c>
       <c r="C34">
-        <v>42.69238077127039</v>
+        <v>42.27436320115919</v>
       </c>
       <c r="D34">
-        <v>42.51398077127039</v>
+        <v>42.66226320115919</v>
       </c>
       <c r="E34">
-        <v>12.3916</v>
+        <v>12.9579</v>
       </c>
       <c r="F34">
-        <v>18.1216</v>
+        <v>18.6879</v>
       </c>
       <c r="G34">
         <v>18.3</v>
@@ -4075,28 +4075,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M34">
-        <v>1.04742848</v>
+        <v>1.08016062</v>
       </c>
       <c r="N34">
-        <v>3.43757152</v>
+        <v>3.404839379999999</v>
       </c>
       <c r="O34">
-        <v>0.9968957407999999</v>
+        <v>0.9874034201999997</v>
       </c>
       <c r="P34">
-        <v>2.4406757792</v>
+        <v>2.4174359598</v>
       </c>
       <c r="Q34">
-        <v>3.3806757792</v>
+        <v>3.3574359598</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3246395968343918</v>
+        <v>0.3278967257689587</v>
       </c>
       <c r="T34">
-        <v>1.705348262969618</v>
+        <v>1.725268458070641</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.281915267379401</v>
+        <v>4.152160259276995</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2332333462652023</v>
+        <v>0.2325796066830182</v>
       </c>
       <c r="C35">
-        <v>42.27436320115919</v>
+        <v>41.85738362545737</v>
       </c>
       <c r="D35">
-        <v>42.66226320115919</v>
+        <v>42.81158362545737</v>
       </c>
       <c r="E35">
-        <v>12.9579</v>
+        <v>13.5242</v>
       </c>
       <c r="F35">
-        <v>18.6879</v>
+        <v>19.2542</v>
       </c>
       <c r="G35">
         <v>18.3</v>
@@ -4157,28 +4157,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M35">
-        <v>1.08016062</v>
+        <v>1.11289276</v>
       </c>
       <c r="N35">
-        <v>3.404839379999999</v>
+        <v>3.372107239999999</v>
       </c>
       <c r="O35">
-        <v>0.9874034201999997</v>
+        <v>0.9779110995999997</v>
       </c>
       <c r="P35">
-        <v>2.4174359598</v>
+        <v>2.3941961404</v>
       </c>
       <c r="Q35">
-        <v>3.3574359598</v>
+        <v>3.3341961404</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3278967257689587</v>
+        <v>0.3312525555803306</v>
       </c>
       <c r="T35">
-        <v>1.725268458070641</v>
+        <v>1.745792295447453</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.152160259276995</v>
+        <v>4.030037898710024</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2325796066830182</v>
+        <v>0.2327956171008341</v>
       </c>
       <c r="C36">
-        <v>41.85738362545737</v>
+        <v>41.24162926813247</v>
       </c>
       <c r="D36">
-        <v>42.81158362545737</v>
+        <v>42.76212926813246</v>
       </c>
       <c r="E36">
-        <v>13.5242</v>
+        <v>14.0905</v>
       </c>
       <c r="F36">
-        <v>19.2542</v>
+        <v>19.8205</v>
       </c>
       <c r="G36">
         <v>18.3</v>
@@ -4239,45 +4239,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M36">
-        <v>1.11289276</v>
+        <v>1.21499665</v>
       </c>
       <c r="N36">
-        <v>3.372107239999999</v>
+        <v>3.27000335</v>
       </c>
       <c r="O36">
-        <v>0.9779110995999997</v>
+        <v>0.9483009714999998</v>
       </c>
       <c r="P36">
-        <v>2.3941961404</v>
+        <v>2.3217023785</v>
       </c>
       <c r="Q36">
-        <v>3.3341961404</v>
+        <v>3.2617023785</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3312525555803306</v>
+        <v>0.334711641693591</v>
       </c>
       <c r="T36">
-        <v>1.745792295447453</v>
+        <v>1.766947635512782</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.29</v>
       </c>
       <c r="W36">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.030037898710024</v>
+        <v>3.691368202537842</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2327956171008341</v>
+        <v>0.23216672751865</v>
       </c>
       <c r="C37">
-        <v>41.24162926813247</v>
+        <v>40.81962893989682</v>
       </c>
       <c r="D37">
-        <v>42.76212926813246</v>
+        <v>42.90642893989682</v>
       </c>
       <c r="E37">
-        <v>14.0905</v>
+        <v>14.6568</v>
       </c>
       <c r="F37">
-        <v>19.8205</v>
+        <v>20.3868</v>
       </c>
       <c r="G37">
         <v>18.3</v>
@@ -4321,28 +4321,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M37">
-        <v>1.21499665</v>
+        <v>1.24971084</v>
       </c>
       <c r="N37">
-        <v>3.27000335</v>
+        <v>3.235289159999999</v>
       </c>
       <c r="O37">
-        <v>0.9483009714999998</v>
+        <v>0.9382338563999998</v>
       </c>
       <c r="P37">
-        <v>2.3217023785</v>
+        <v>2.2970553036</v>
       </c>
       <c r="Q37">
-        <v>3.2617023785</v>
+        <v>3.2370553036</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.334711641693591</v>
+        <v>0.3382788242478906</v>
       </c>
       <c r="T37">
-        <v>1.766947635512782</v>
+        <v>1.788764079955152</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.691368202537842</v>
+        <v>3.588830196911791</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.23216672751865</v>
+        <v>0.2322733979364659</v>
       </c>
       <c r="C38">
-        <v>40.81962893989682</v>
+        <v>40.22878470595968</v>
       </c>
       <c r="D38">
-        <v>42.90642893989681</v>
+        <v>42.88188470595967</v>
       </c>
       <c r="E38">
-        <v>14.6568</v>
+        <v>15.2231</v>
       </c>
       <c r="F38">
-        <v>20.3868</v>
+        <v>20.9531</v>
       </c>
       <c r="G38">
         <v>18.3</v>
@@ -4403,45 +4403,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M38">
-        <v>1.24971084</v>
+        <v>1.34309371</v>
       </c>
       <c r="N38">
-        <v>3.23528916</v>
+        <v>3.14190629</v>
       </c>
       <c r="O38">
-        <v>0.9382338563999999</v>
+        <v>0.9111528240999999</v>
       </c>
       <c r="P38">
-        <v>2.2970553036</v>
+        <v>2.2307534659</v>
       </c>
       <c r="Q38">
-        <v>3.2370553036</v>
+        <v>3.1707534659</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3382788242478906</v>
+        <v>0.341959250692803</v>
       </c>
       <c r="T38">
-        <v>1.788764079955152</v>
+        <v>1.811273109935376</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.29</v>
       </c>
       <c r="W38">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.588830196911792</v>
+        <v>3.339305341546123</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2322733979364659</v>
+        <v>0.2316643883542818</v>
       </c>
       <c r="C39">
-        <v>40.22878470595968</v>
+        <v>39.80299294919703</v>
       </c>
       <c r="D39">
-        <v>42.88188470595967</v>
+        <v>43.02239294919702</v>
       </c>
       <c r="E39">
-        <v>15.2231</v>
+        <v>15.7894</v>
       </c>
       <c r="F39">
-        <v>20.9531</v>
+        <v>21.5194</v>
       </c>
       <c r="G39">
         <v>18.3</v>
@@ -4485,28 +4485,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M39">
-        <v>1.34309371</v>
+        <v>1.37939354</v>
       </c>
       <c r="N39">
-        <v>3.14190629</v>
+        <v>3.10560646</v>
       </c>
       <c r="O39">
-        <v>0.9111528240999999</v>
+        <v>0.9006258733999999</v>
       </c>
       <c r="P39">
-        <v>2.2307534659</v>
+        <v>2.2049805866</v>
       </c>
       <c r="Q39">
-        <v>3.1707534659</v>
+        <v>3.1449805866</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.341959250692803</v>
+        <v>0.3457584005714222</v>
       </c>
       <c r="T39">
-        <v>1.811273109935376</v>
+        <v>1.834508237656897</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.339305341546123</v>
+        <v>3.251428885189646</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2316643883542818</v>
+        <v>0.2310553787720976</v>
       </c>
       <c r="C40">
-        <v>39.80299294919703</v>
+        <v>39.37812500762477</v>
       </c>
       <c r="D40">
-        <v>43.02239294919702</v>
+        <v>43.16382500762478</v>
       </c>
       <c r="E40">
-        <v>15.7894</v>
+        <v>16.3557</v>
       </c>
       <c r="F40">
-        <v>21.5194</v>
+        <v>22.0857</v>
       </c>
       <c r="G40">
         <v>18.3</v>
@@ -4567,28 +4567,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M40">
-        <v>1.37939354</v>
+        <v>1.41569337</v>
       </c>
       <c r="N40">
-        <v>3.10560646</v>
+        <v>3.069306629999999</v>
       </c>
       <c r="O40">
-        <v>0.9006258733999999</v>
+        <v>0.8900989226999998</v>
       </c>
       <c r="P40">
-        <v>2.2049805866</v>
+        <v>2.1792077073</v>
       </c>
       <c r="Q40">
-        <v>3.1449805866</v>
+        <v>3.1192077073</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3457584005714222</v>
+        <v>0.3496821127411437</v>
       </c>
       <c r="T40">
-        <v>1.834508237656897</v>
+        <v>1.858505172844697</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.251428885189646</v>
+        <v>3.168058913774527</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2310553787720976</v>
+        <v>0.2304463691899136</v>
       </c>
       <c r="C41">
-        <v>39.37812500762477</v>
+        <v>38.95419002215871</v>
       </c>
       <c r="D41">
-        <v>43.16382500762478</v>
+        <v>43.30619002215871</v>
       </c>
       <c r="E41">
-        <v>16.3557</v>
+        <v>16.922</v>
       </c>
       <c r="F41">
-        <v>22.0857</v>
+        <v>22.652</v>
       </c>
       <c r="G41">
         <v>18.3</v>
@@ -4649,28 +4649,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M41">
-        <v>1.41569337</v>
+        <v>1.4519932</v>
       </c>
       <c r="N41">
-        <v>3.069306629999999</v>
+        <v>3.033006799999999</v>
       </c>
       <c r="O41">
-        <v>0.8900989226999998</v>
+        <v>0.8795719719999997</v>
       </c>
       <c r="P41">
-        <v>2.1792077073</v>
+        <v>2.153434827999999</v>
       </c>
       <c r="Q41">
-        <v>3.1192077073</v>
+        <v>3.093434827999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3496821127411437</v>
+        <v>0.3537366153165226</v>
       </c>
       <c r="T41">
-        <v>1.858505172844697</v>
+        <v>1.883302005872091</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.168058913774527</v>
+        <v>3.088857440930163</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2304463691899136</v>
+        <v>0.2298373596077295</v>
       </c>
       <c r="C42">
-        <v>38.95419002215871</v>
+        <v>38.53119725470972</v>
       </c>
       <c r="D42">
-        <v>43.30619002215871</v>
+        <v>43.44949725470973</v>
       </c>
       <c r="E42">
-        <v>16.922</v>
+        <v>17.4883</v>
       </c>
       <c r="F42">
-        <v>22.652</v>
+        <v>23.2183</v>
       </c>
       <c r="G42">
         <v>18.3</v>
@@ -4731,28 +4731,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M42">
-        <v>1.4519932</v>
+        <v>1.48829303</v>
       </c>
       <c r="N42">
-        <v>3.033006799999999</v>
+        <v>2.996706969999999</v>
       </c>
       <c r="O42">
-        <v>0.8795719719999997</v>
+        <v>0.8690450212999997</v>
       </c>
       <c r="P42">
-        <v>2.153434827999999</v>
+        <v>2.127661948699999</v>
       </c>
       <c r="Q42">
-        <v>3.093434827999999</v>
+        <v>3.067661948699999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3537366153165226</v>
+        <v>0.3579285586571686</v>
       </c>
       <c r="T42">
-        <v>1.883302005872091</v>
+        <v>1.908939409510583</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.088857440930163</v>
+        <v>3.013519454566013</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2298373596077295</v>
+        <v>0.2315543100255454</v>
       </c>
       <c r="C43">
-        <v>38.53119725470972</v>
+        <v>37.56328809444257</v>
       </c>
       <c r="D43">
-        <v>43.44949725470973</v>
+        <v>43.04788809444257</v>
       </c>
       <c r="E43">
-        <v>17.4883</v>
+        <v>18.0546</v>
       </c>
       <c r="F43">
-        <v>23.2183</v>
+        <v>23.7846</v>
       </c>
       <c r="G43">
         <v>18.3</v>
@@ -4813,45 +4813,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M43">
-        <v>1.48829303</v>
+        <v>1.71011274</v>
       </c>
       <c r="N43">
-        <v>2.996706969999999</v>
+        <v>2.774887259999999</v>
       </c>
       <c r="O43">
-        <v>0.8690450212999997</v>
+        <v>0.8047173053999996</v>
       </c>
       <c r="P43">
-        <v>2.127661948699999</v>
+        <v>1.970169954599999</v>
       </c>
       <c r="Q43">
-        <v>3.067661948699999</v>
+        <v>2.910169954599999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3579285586571686</v>
+        <v>0.3622650517681816</v>
       </c>
       <c r="T43">
-        <v>1.908939409510583</v>
+        <v>1.935460861550402</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.29</v>
       </c>
       <c r="W43">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.013519454566013</v>
+        <v>2.622634107737247</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2315543100255454</v>
+        <v>0.2310006804433613</v>
       </c>
       <c r="C44">
-        <v>37.56328809444257</v>
+        <v>37.12567328200549</v>
       </c>
       <c r="D44">
-        <v>43.04788809444256</v>
+        <v>43.17657328200549</v>
       </c>
       <c r="E44">
-        <v>18.0546</v>
+        <v>18.6209</v>
       </c>
       <c r="F44">
-        <v>23.7846</v>
+        <v>24.3509</v>
       </c>
       <c r="G44">
         <v>18.3</v>
@@ -4895,28 +4895,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M44">
-        <v>1.71011274</v>
+        <v>1.75082971</v>
       </c>
       <c r="N44">
-        <v>2.774887259999999</v>
+        <v>2.734170289999999</v>
       </c>
       <c r="O44">
-        <v>0.8047173053999997</v>
+        <v>0.7929093840999998</v>
       </c>
       <c r="P44">
-        <v>1.9701699546</v>
+        <v>1.9412609059</v>
       </c>
       <c r="Q44">
-        <v>2.9101699546</v>
+        <v>2.8812609059</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3622650517681816</v>
+        <v>0.3667537025322127</v>
       </c>
       <c r="T44">
-        <v>1.935460861550402</v>
+        <v>1.962912890854777</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.622634107737247</v>
+        <v>2.561642616859637</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2310006804433613</v>
+        <v>0.2304470508611772</v>
       </c>
       <c r="C45">
-        <v>37.12567328200549</v>
+        <v>36.68883014641125</v>
       </c>
       <c r="D45">
-        <v>43.17657328200549</v>
+        <v>43.30603014641124</v>
       </c>
       <c r="E45">
-        <v>18.6209</v>
+        <v>19.1872</v>
       </c>
       <c r="F45">
-        <v>24.3509</v>
+        <v>24.9172</v>
       </c>
       <c r="G45">
         <v>18.3</v>
@@ -4977,28 +4977,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M45">
-        <v>1.75082971</v>
+        <v>1.79154668</v>
       </c>
       <c r="N45">
-        <v>2.734170289999999</v>
+        <v>2.69345332</v>
       </c>
       <c r="O45">
-        <v>0.7929093840999998</v>
+        <v>0.7811014627999998</v>
       </c>
       <c r="P45">
-        <v>1.9412609059</v>
+        <v>1.9123518572</v>
       </c>
       <c r="Q45">
-        <v>2.8812609059</v>
+        <v>2.8523518572</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3667537025322127</v>
+        <v>0.3714026622521021</v>
       </c>
       <c r="T45">
-        <v>1.962912890854777</v>
+        <v>1.991345349777164</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.561642616859637</v>
+        <v>2.503423466476463</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2304470508611772</v>
+        <v>0.231139471278993</v>
       </c>
       <c r="C46">
-        <v>36.68883014641125</v>
+        <v>35.96074065127026</v>
       </c>
       <c r="D46">
-        <v>43.30603014641124</v>
+        <v>43.14424065127026</v>
       </c>
       <c r="E46">
-        <v>19.1872</v>
+        <v>19.7535</v>
       </c>
       <c r="F46">
-        <v>24.9172</v>
+        <v>25.4835</v>
       </c>
       <c r="G46">
         <v>18.3</v>
@@ -5059,45 +5059,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M46">
-        <v>1.79154668</v>
+        <v>1.9316493</v>
       </c>
       <c r="N46">
-        <v>2.69345332</v>
+        <v>2.553350699999999</v>
       </c>
       <c r="O46">
-        <v>0.7811014627999998</v>
+        <v>0.7404717029999998</v>
       </c>
       <c r="P46">
-        <v>1.9123518572</v>
+        <v>1.812878996999999</v>
       </c>
       <c r="Q46">
-        <v>2.8523518572</v>
+        <v>2.752878996999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3714026622521021</v>
+        <v>0.3762206750527146</v>
       </c>
       <c r="T46">
-        <v>1.991345349777164</v>
+        <v>2.02081171629673</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.29</v>
       </c>
       <c r="W46">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.503423466476463</v>
+        <v>2.321850037685412</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.231139471278993</v>
+        <v>0.230613531696809</v>
       </c>
       <c r="C47">
-        <v>35.96074065127026</v>
+        <v>35.51721988552571</v>
       </c>
       <c r="D47">
-        <v>43.14424065127026</v>
+        <v>43.26701988552571</v>
       </c>
       <c r="E47">
-        <v>19.7535</v>
+        <v>20.3198</v>
       </c>
       <c r="F47">
-        <v>25.4835</v>
+        <v>26.0498</v>
       </c>
       <c r="G47">
         <v>18.3</v>
@@ -5141,28 +5141,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M47">
-        <v>1.9316493</v>
+        <v>1.97457484</v>
       </c>
       <c r="N47">
-        <v>2.553350699999999</v>
+        <v>2.51042516</v>
       </c>
       <c r="O47">
-        <v>0.7404717029999998</v>
+        <v>0.7280232963999999</v>
       </c>
       <c r="P47">
-        <v>1.812878996999999</v>
+        <v>1.7824018636</v>
       </c>
       <c r="Q47">
-        <v>2.752878996999999</v>
+        <v>2.7224018636</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3762206750527146</v>
+        <v>0.3812171327718684</v>
       </c>
       <c r="T47">
-        <v>2.02081171629673</v>
+        <v>2.051369429724427</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.321850037685412</v>
+        <v>2.271375036866164</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.230613531696809</v>
+        <v>0.2300875921146249</v>
       </c>
       <c r="C48">
-        <v>35.51721988552571</v>
+        <v>35.07439992072412</v>
       </c>
       <c r="D48">
-        <v>43.26701988552571</v>
+        <v>43.39049992072412</v>
       </c>
       <c r="E48">
-        <v>20.3198</v>
+        <v>20.8861</v>
       </c>
       <c r="F48">
-        <v>26.0498</v>
+        <v>26.6161</v>
       </c>
       <c r="G48">
         <v>18.3</v>
@@ -5223,28 +5223,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M48">
-        <v>1.97457484</v>
+        <v>2.01750038</v>
       </c>
       <c r="N48">
-        <v>2.51042516</v>
+        <v>2.467499619999999</v>
       </c>
       <c r="O48">
-        <v>0.7280232963999999</v>
+        <v>0.7155748897999998</v>
       </c>
       <c r="P48">
-        <v>1.7824018636</v>
+        <v>1.7519247302</v>
       </c>
       <c r="Q48">
-        <v>2.7224018636</v>
+        <v>2.691924730199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3812171327718684</v>
+        <v>0.3864021360653299</v>
       </c>
       <c r="T48">
-        <v>2.051369429724427</v>
+        <v>2.083080264413547</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.271375036866164</v>
+        <v>2.223047908422203</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2300875921146249</v>
+        <v>0.2295616525324408</v>
       </c>
       <c r="C49">
-        <v>35.07439992072412</v>
+        <v>34.6322867740995</v>
       </c>
       <c r="D49">
-        <v>43.39049992072412</v>
+        <v>43.5146867740995</v>
       </c>
       <c r="E49">
-        <v>20.8861</v>
+        <v>21.4524</v>
       </c>
       <c r="F49">
-        <v>26.6161</v>
+        <v>27.1824</v>
       </c>
       <c r="G49">
         <v>18.3</v>
@@ -5305,28 +5305,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M49">
-        <v>2.01750038</v>
+        <v>2.06042592</v>
       </c>
       <c r="N49">
-        <v>2.467499619999999</v>
+        <v>2.424574079999999</v>
       </c>
       <c r="O49">
-        <v>0.7155748897999998</v>
+        <v>0.7031264831999997</v>
       </c>
       <c r="P49">
-        <v>1.7519247302</v>
+        <v>1.7214475968</v>
       </c>
       <c r="Q49">
-        <v>2.691924730199999</v>
+        <v>2.6614475968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3864021360653299</v>
+        <v>0.391786562562386</v>
       </c>
       <c r="T49">
-        <v>2.083080264413547</v>
+        <v>2.11601074659071</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.223047908422203</v>
+        <v>2.176734410330074</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2295616525324407</v>
+        <v>0.2290357129502566</v>
       </c>
       <c r="C50">
-        <v>34.63228677409951</v>
+        <v>34.1908865319707</v>
       </c>
       <c r="D50">
-        <v>43.51468677409951</v>
+        <v>43.63958653197071</v>
       </c>
       <c r="E50">
-        <v>21.4524</v>
+        <v>22.0187</v>
       </c>
       <c r="F50">
-        <v>27.1824</v>
+        <v>27.7487</v>
       </c>
       <c r="G50">
         <v>18.3</v>
@@ -5387,28 +5387,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M50">
-        <v>2.06042592</v>
+        <v>2.10335146</v>
       </c>
       <c r="N50">
-        <v>2.424574079999999</v>
+        <v>2.38164854</v>
       </c>
       <c r="O50">
-        <v>0.7031264831999997</v>
+        <v>0.6906780765999998</v>
       </c>
       <c r="P50">
-        <v>1.7214475968</v>
+        <v>1.6909704634</v>
       </c>
       <c r="Q50">
-        <v>2.6614475968</v>
+        <v>2.6309704634</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.391786562562386</v>
+        <v>0.3973821430397189</v>
       </c>
       <c r="T50">
-        <v>2.11601074659071</v>
+        <v>2.150232620225801</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.176734410330074</v>
+        <v>2.132311259098848</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2290357129502566</v>
+        <v>0.2285097733680725</v>
       </c>
       <c r="C51">
-        <v>34.1908865319707</v>
+        <v>33.75020535073568</v>
       </c>
       <c r="D51">
-        <v>43.63958653197071</v>
+        <v>43.76520535073568</v>
       </c>
       <c r="E51">
-        <v>22.0187</v>
+        <v>22.585</v>
       </c>
       <c r="F51">
-        <v>27.7487</v>
+        <v>28.315</v>
       </c>
       <c r="G51">
         <v>18.3</v>
@@ -5469,28 +5469,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M51">
-        <v>2.10335146</v>
+        <v>2.146277</v>
       </c>
       <c r="N51">
-        <v>2.38164854</v>
+        <v>2.338722999999999</v>
       </c>
       <c r="O51">
-        <v>0.6906780765999998</v>
+        <v>0.6782296699999998</v>
       </c>
       <c r="P51">
-        <v>1.6909704634</v>
+        <v>1.66049333</v>
       </c>
       <c r="Q51">
-        <v>2.6309704634</v>
+        <v>2.600493329999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3973821430397189</v>
+        <v>0.403201546736145</v>
       </c>
       <c r="T51">
-        <v>2.150232620225801</v>
+        <v>2.185823368806296</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.132311259098848</v>
+        <v>2.089665033916871</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2285097733680725</v>
+        <v>0.2279838337858884</v>
       </c>
       <c r="C52">
-        <v>33.75020535073568</v>
+        <v>33.31024945788306</v>
       </c>
       <c r="D52">
-        <v>43.76520535073568</v>
+        <v>43.89154945788305</v>
       </c>
       <c r="E52">
-        <v>22.585</v>
+        <v>23.1513</v>
       </c>
       <c r="F52">
-        <v>28.315</v>
+        <v>28.8813</v>
       </c>
       <c r="G52">
         <v>18.3</v>
@@ -5551,28 +5551,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M52">
-        <v>2.146277</v>
+        <v>2.18920254</v>
       </c>
       <c r="N52">
-        <v>2.338722999999999</v>
+        <v>2.295797459999999</v>
       </c>
       <c r="O52">
-        <v>0.6782296699999998</v>
+        <v>0.6657812633999998</v>
       </c>
       <c r="P52">
-        <v>1.66049333</v>
+        <v>1.6300161966</v>
       </c>
       <c r="Q52">
-        <v>2.600493329999999</v>
+        <v>2.570016196599999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.403201546736145</v>
+        <v>0.409258477114058</v>
       </c>
       <c r="T52">
-        <v>2.185823368806296</v>
+        <v>2.222866801002321</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.089665033916871</v>
+        <v>2.048691209722422</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2279838337858884</v>
+        <v>0.2274578942037043</v>
       </c>
       <c r="C53">
-        <v>33.31024945788306</v>
+        <v>32.87102515302135</v>
       </c>
       <c r="D53">
-        <v>43.89154945788305</v>
+        <v>44.01862515302134</v>
       </c>
       <c r="E53">
-        <v>23.1513</v>
+        <v>23.7176</v>
       </c>
       <c r="F53">
-        <v>28.8813</v>
+        <v>29.4476</v>
       </c>
       <c r="G53">
         <v>18.3</v>
@@ -5633,28 +5633,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M53">
-        <v>2.18920254</v>
+        <v>2.23212808</v>
       </c>
       <c r="N53">
-        <v>2.295797459999999</v>
+        <v>2.25287192</v>
       </c>
       <c r="O53">
-        <v>0.6657812633999998</v>
+        <v>0.6533328567999999</v>
       </c>
       <c r="P53">
-        <v>1.6300161966</v>
+        <v>1.5995390632</v>
       </c>
       <c r="Q53">
-        <v>2.570016196599999</v>
+        <v>2.539539063199999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.409258477114058</v>
+        <v>0.4155677795910507</v>
       </c>
       <c r="T53">
-        <v>2.222866801002321</v>
+        <v>2.261453709539847</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.048691209722422</v>
+        <v>2.009293301843145</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2274578942037043</v>
+        <v>0.2322754146215202</v>
       </c>
       <c r="C54">
-        <v>32.87102515302135</v>
+        <v>31.16752094908232</v>
       </c>
       <c r="D54">
-        <v>44.01862515302134</v>
+        <v>42.88142094908232</v>
       </c>
       <c r="E54">
-        <v>23.7176</v>
+        <v>24.2839</v>
       </c>
       <c r="F54">
-        <v>29.4476</v>
+        <v>30.0139</v>
       </c>
       <c r="G54">
         <v>18.3</v>
@@ -5715,45 +5715,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M54">
-        <v>2.23212808</v>
+        <v>2.701251</v>
       </c>
       <c r="N54">
-        <v>2.25287192</v>
+        <v>1.783748999999999</v>
       </c>
       <c r="O54">
-        <v>0.6533328567999999</v>
+        <v>0.5172872099999998</v>
       </c>
       <c r="P54">
-        <v>1.5995390632</v>
+        <v>1.26646179</v>
       </c>
       <c r="Q54">
-        <v>2.539539063199999</v>
+        <v>2.20646179</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4155677795910507</v>
+        <v>0.4221455630245111</v>
       </c>
       <c r="T54">
-        <v>2.261453709539847</v>
+        <v>2.301682614185353</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
         <v>0.29</v>
       </c>
       <c r="W54">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.009293301843145</v>
+        <v>1.660341819401455</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2322754146215202</v>
+        <v>0.2318502950393361</v>
       </c>
       <c r="C55">
-        <v>31.16752094908232</v>
+        <v>30.69920376471548</v>
       </c>
       <c r="D55">
-        <v>42.88142094908232</v>
+        <v>42.97940376471549</v>
       </c>
       <c r="E55">
-        <v>24.2839</v>
+        <v>24.8502</v>
       </c>
       <c r="F55">
-        <v>30.0139</v>
+        <v>30.5802</v>
       </c>
       <c r="G55">
         <v>18.3</v>
@@ -5797,28 +5797,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M55">
-        <v>2.701251</v>
+        <v>2.752218</v>
       </c>
       <c r="N55">
-        <v>1.783748999999999</v>
+        <v>1.732782</v>
       </c>
       <c r="O55">
-        <v>0.5172872099999998</v>
+        <v>0.5025067799999999</v>
       </c>
       <c r="P55">
-        <v>1.26646179</v>
+        <v>1.23027522</v>
       </c>
       <c r="Q55">
-        <v>2.20646179</v>
+        <v>2.17027522</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4221455630245111</v>
+        <v>0.429009337042035</v>
       </c>
       <c r="T55">
-        <v>2.301682614185353</v>
+        <v>2.343660601641533</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.660341819401455</v>
+        <v>1.629594748671799</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2318502950393361</v>
+        <v>0.231425175457152</v>
       </c>
       <c r="C56">
-        <v>30.69920376471548</v>
+        <v>30.23133538168759</v>
       </c>
       <c r="D56">
-        <v>42.97940376471549</v>
+        <v>43.07783538168758</v>
       </c>
       <c r="E56">
-        <v>24.8502</v>
+        <v>25.4165</v>
       </c>
       <c r="F56">
-        <v>30.5802</v>
+        <v>31.1465</v>
       </c>
       <c r="G56">
         <v>18.3</v>
@@ -5879,28 +5879,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M56">
-        <v>2.752218</v>
+        <v>2.803185</v>
       </c>
       <c r="N56">
-        <v>1.732782</v>
+        <v>1.681814999999999</v>
       </c>
       <c r="O56">
-        <v>0.5025067799999999</v>
+        <v>0.4877263499999998</v>
       </c>
       <c r="P56">
-        <v>1.23027522</v>
+        <v>1.19408865</v>
       </c>
       <c r="Q56">
-        <v>2.17027522</v>
+        <v>2.13408865</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.429009337042035</v>
+        <v>0.4361781676825601</v>
       </c>
       <c r="T56">
-        <v>2.343660601641533</v>
+        <v>2.3875042774291</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.629594748671799</v>
+        <v>1.599965753241402</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.231425175457152</v>
+        <v>0.2310000558749679</v>
       </c>
       <c r="C57">
-        <v>30.23133538168759</v>
+        <v>29.76391889061711</v>
       </c>
       <c r="D57">
-        <v>43.07783538168758</v>
+        <v>43.1767188906171</v>
       </c>
       <c r="E57">
-        <v>25.4165</v>
+        <v>25.9828</v>
       </c>
       <c r="F57">
-        <v>31.1465</v>
+        <v>31.7128</v>
       </c>
       <c r="G57">
         <v>18.3</v>
@@ -5961,28 +5961,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M57">
-        <v>2.803185</v>
+        <v>2.854152</v>
       </c>
       <c r="N57">
-        <v>1.681814999999999</v>
+        <v>1.630847999999999</v>
       </c>
       <c r="O57">
-        <v>0.4877263499999998</v>
+        <v>0.4729459199999998</v>
       </c>
       <c r="P57">
-        <v>1.19408865</v>
+        <v>1.15790208</v>
       </c>
       <c r="Q57">
-        <v>2.13408865</v>
+        <v>2.097902079999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4361781676825601</v>
+        <v>0.4436728542612907</v>
       </c>
       <c r="T57">
-        <v>2.3875042774291</v>
+        <v>2.433340847570646</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.599965753241402</v>
+        <v>1.571394936219234</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2310000558749679</v>
+        <v>0.2305749362927838</v>
       </c>
       <c r="C58">
-        <v>29.76391889061711</v>
+        <v>29.29695741056537</v>
       </c>
       <c r="D58">
-        <v>43.1767188906171</v>
+        <v>43.27605741056537</v>
       </c>
       <c r="E58">
-        <v>25.9828</v>
+        <v>26.5491</v>
       </c>
       <c r="F58">
-        <v>31.7128</v>
+        <v>32.2791</v>
       </c>
       <c r="G58">
         <v>18.3</v>
@@ -6043,28 +6043,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M58">
-        <v>2.854152</v>
+        <v>2.905119</v>
       </c>
       <c r="N58">
-        <v>1.630847999999999</v>
+        <v>1.579880999999999</v>
       </c>
       <c r="O58">
-        <v>0.4729459199999998</v>
+        <v>0.4581654899999998</v>
       </c>
       <c r="P58">
-        <v>1.15790208</v>
+        <v>1.12171551</v>
       </c>
       <c r="Q58">
-        <v>2.097902079999999</v>
+        <v>2.06171551</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4436728542612907</v>
+        <v>0.4515161309134507</v>
       </c>
       <c r="T58">
-        <v>2.433340847570646</v>
+        <v>2.481309351207147</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.571394936219234</v>
+        <v>1.543826604004862</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2305749362927838</v>
+        <v>0.2301498167105997</v>
       </c>
       <c r="C59">
-        <v>29.29695741056537</v>
+        <v>28.83045408936455</v>
       </c>
       <c r="D59">
-        <v>43.27605741056537</v>
+        <v>43.37585408936454</v>
       </c>
       <c r="E59">
-        <v>26.5491</v>
+        <v>27.1154</v>
       </c>
       <c r="F59">
-        <v>32.2791</v>
+        <v>32.8454</v>
       </c>
       <c r="G59">
         <v>18.3</v>
@@ -6125,28 +6125,28 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M59">
-        <v>2.905119</v>
+        <v>2.956086</v>
       </c>
       <c r="N59">
-        <v>1.579880999999999</v>
+        <v>1.528914</v>
       </c>
       <c r="O59">
-        <v>0.4581654899999998</v>
+        <v>0.4433850599999999</v>
       </c>
       <c r="P59">
-        <v>1.12171551</v>
+        <v>1.08552894</v>
       </c>
       <c r="Q59">
-        <v>2.06171551</v>
+        <v>2.02552894</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4515161309134507</v>
+        <v>0.4597328969299992</v>
       </c>
       <c r="T59">
-        <v>2.481309351207147</v>
+        <v>2.53156206930253</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.543826604004862</v>
+        <v>1.517208903935813</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2301498167105997</v>
+        <v>0.2587292145212099</v>
       </c>
       <c r="C60">
-        <v>28.83045408936454</v>
+        <v>22.442239082622</v>
       </c>
       <c r="D60">
-        <v>43.37585408936454</v>
+        <v>37.55393908262199</v>
       </c>
       <c r="E60">
-        <v>27.1154</v>
+        <v>27.6817</v>
       </c>
       <c r="F60">
-        <v>32.8454</v>
+        <v>33.4117</v>
       </c>
       <c r="G60">
         <v>18.3</v>
@@ -6207,45 +6207,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M60">
-        <v>2.956086</v>
+        <v>4.90483756</v>
       </c>
       <c r="N60">
-        <v>1.528914</v>
+        <v>-0.4198375600000004</v>
       </c>
       <c r="O60">
-        <v>0.4433850599999999</v>
+        <v>-0.1217528924000001</v>
       </c>
       <c r="P60">
-        <v>1.08552894</v>
+        <v>-0.2980846676000003</v>
       </c>
       <c r="Q60">
-        <v>2.02552894</v>
+        <v>0.6419153323999996</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4597328969299992</v>
+        <v>0.4758163973390007</v>
       </c>
       <c r="T60">
-        <v>2.53156206930253</v>
+        <v>2.629926755653916</v>
       </c>
       <c r="U60">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.29</v>
+        <v>0.2651769776449028</v>
       </c>
       <c r="W60">
-        <v>0.0639</v>
+        <v>0.1078720196817283</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.517208903935813</v>
+        <v>0.9144033711893202</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2587292145212099</v>
+        <v>0.25973921452121</v>
       </c>
       <c r="C61">
-        <v>22.442239082622</v>
+        <v>21.6986481705359</v>
       </c>
       <c r="D61">
-        <v>37.55393908262199</v>
+        <v>37.37664817053589</v>
       </c>
       <c r="E61">
-        <v>27.6817</v>
+        <v>28.24799999999999</v>
       </c>
       <c r="F61">
-        <v>33.4117</v>
+        <v>33.97799999999999</v>
       </c>
       <c r="G61">
         <v>18.3</v>
@@ -6289,37 +6289,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M61">
-        <v>4.90483756</v>
+        <v>4.9879704</v>
       </c>
       <c r="N61">
-        <v>-0.4198375600000004</v>
+        <v>-0.5029704000000006</v>
       </c>
       <c r="O61">
-        <v>-0.1217528924000001</v>
+        <v>-0.1458614160000002</v>
       </c>
       <c r="P61">
-        <v>-0.2980846676000003</v>
+        <v>-0.3571089840000005</v>
       </c>
       <c r="Q61">
-        <v>0.6419153323999996</v>
+        <v>0.5828910159999995</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4758163973390007</v>
+        <v>0.4865668072724758</v>
       </c>
       <c r="T61">
-        <v>2.629926755653916</v>
+        <v>2.695674924545264</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2651769776449028</v>
+        <v>0.2607573613508211</v>
       </c>
       <c r="W61">
-        <v>0.1078720196817283</v>
+        <v>0.1085208193536995</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9144033711893202</v>
+        <v>0.8991633150028315</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.25973921452121</v>
+        <v>0.26074921452121</v>
       </c>
       <c r="C62">
-        <v>21.6986481705359</v>
+        <v>20.95672336196737</v>
       </c>
       <c r="D62">
-        <v>37.37664817053589</v>
+        <v>37.20102336196737</v>
       </c>
       <c r="E62">
-        <v>28.24799999999999</v>
+        <v>28.8143</v>
       </c>
       <c r="F62">
-        <v>33.97799999999999</v>
+        <v>34.5443</v>
       </c>
       <c r="G62">
         <v>18.3</v>
@@ -6371,37 +6371,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M62">
-        <v>4.9879704</v>
+        <v>5.07110324</v>
       </c>
       <c r="N62">
-        <v>-0.5029704000000006</v>
+        <v>-0.5861032400000008</v>
       </c>
       <c r="O62">
-        <v>-0.1458614160000002</v>
+        <v>-0.1699699396000002</v>
       </c>
       <c r="P62">
-        <v>-0.3571089840000005</v>
+        <v>-0.4161333004000006</v>
       </c>
       <c r="Q62">
-        <v>0.5828910159999995</v>
+        <v>0.5238666995999994</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4865668072724758</v>
+        <v>0.4978685202794623</v>
       </c>
       <c r="T62">
-        <v>2.695674924545264</v>
+        <v>2.764794794405399</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2607573613508211</v>
+        <v>0.2564826505090044</v>
       </c>
       <c r="W62">
-        <v>0.1085208193536995</v>
+        <v>0.1091483469052782</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8991633150028315</v>
+        <v>0.8844229327896703</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.26074921452121</v>
+        <v>0.26175921452121</v>
       </c>
       <c r="C63">
-        <v>20.95672336196737</v>
+        <v>20.21644128077261</v>
       </c>
       <c r="D63">
-        <v>37.20102336196737</v>
+        <v>37.02704128077261</v>
       </c>
       <c r="E63">
-        <v>28.8143</v>
+        <v>29.3806</v>
       </c>
       <c r="F63">
-        <v>34.5443</v>
+        <v>35.1106</v>
       </c>
       <c r="G63">
         <v>18.3</v>
@@ -6453,37 +6453,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M63">
-        <v>5.07110324</v>
+        <v>5.15423608</v>
       </c>
       <c r="N63">
-        <v>-0.5861032400000008</v>
+        <v>-0.669236080000001</v>
       </c>
       <c r="O63">
-        <v>-0.1699699396000002</v>
+        <v>-0.1940784632000003</v>
       </c>
       <c r="P63">
-        <v>-0.4161333004000006</v>
+        <v>-0.4751576168000007</v>
       </c>
       <c r="Q63">
-        <v>0.5238666995999994</v>
+        <v>0.4648423831999992</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4978685202794623</v>
+        <v>0.5097650602868166</v>
       </c>
       <c r="T63">
-        <v>2.764794794405399</v>
+        <v>2.837552552152909</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2564826505090044</v>
+        <v>0.2523458335653108</v>
       </c>
       <c r="W63">
-        <v>0.1091483469052782</v>
+        <v>0.1097556316326124</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8844229327896703</v>
+        <v>0.8701580467769336</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.26175921452121</v>
+        <v>0.26276921452121</v>
       </c>
       <c r="C64">
-        <v>20.21644128077261</v>
+        <v>19.47777898607514</v>
       </c>
       <c r="D64">
-        <v>37.02704128077261</v>
+        <v>36.85467898607514</v>
       </c>
       <c r="E64">
-        <v>29.3806</v>
+        <v>29.9469</v>
       </c>
       <c r="F64">
-        <v>35.1106</v>
+        <v>35.6769</v>
       </c>
       <c r="G64">
         <v>18.3</v>
@@ -6535,37 +6535,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M64">
-        <v>5.15423608</v>
+        <v>5.23736892</v>
       </c>
       <c r="N64">
-        <v>-0.669236080000001</v>
+        <v>-0.7523689200000003</v>
       </c>
       <c r="O64">
-        <v>-0.1940784632000003</v>
+        <v>-0.2181869868000001</v>
       </c>
       <c r="P64">
-        <v>-0.4751576168000007</v>
+        <v>-0.5341819332000002</v>
       </c>
       <c r="Q64">
-        <v>0.4648423831999992</v>
+        <v>0.4058180667999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.5097650602868166</v>
+        <v>0.5223046565107846</v>
       </c>
       <c r="T64">
-        <v>2.837552552152909</v>
+        <v>2.914243161670556</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2523458335653108</v>
+        <v>0.2483403441436391</v>
       </c>
       <c r="W64">
-        <v>0.1097556316326124</v>
+        <v>0.1103436374797138</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8701580467769336</v>
+        <v>0.856346014288411</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.26276921452121</v>
+        <v>0.26377921452121</v>
       </c>
       <c r="C65">
-        <v>19.47777898607514</v>
+        <v>18.74071396218195</v>
       </c>
       <c r="D65">
-        <v>36.85467898607514</v>
+        <v>36.68391396218194</v>
       </c>
       <c r="E65">
-        <v>29.9469</v>
+        <v>30.51319999999999</v>
       </c>
       <c r="F65">
-        <v>35.6769</v>
+        <v>36.24319999999999</v>
       </c>
       <c r="G65">
         <v>18.3</v>
@@ -6617,37 +6617,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M65">
-        <v>5.23736892</v>
+        <v>5.32050176</v>
       </c>
       <c r="N65">
-        <v>-0.7523689200000003</v>
+        <v>-0.8355017600000005</v>
       </c>
       <c r="O65">
-        <v>-0.2181869868000001</v>
+        <v>-0.2422955104000001</v>
       </c>
       <c r="P65">
-        <v>-0.5341819332000002</v>
+        <v>-0.5932062496000003</v>
       </c>
       <c r="Q65">
-        <v>0.4058180667999998</v>
+        <v>0.3467937503999996</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5223046565107846</v>
+        <v>0.5355408969694175</v>
       </c>
       <c r="T65">
-        <v>2.914243161670556</v>
+        <v>2.995194360605849</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2483403441436391</v>
+        <v>0.2444600262663948</v>
       </c>
       <c r="W65">
-        <v>0.1103436374797138</v>
+        <v>0.1109132681440933</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.856346014288411</v>
+        <v>0.8429656078151545</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.26377921452121</v>
+        <v>0.26478921452121</v>
       </c>
       <c r="C66">
-        <v>18.74071396218195</v>
+        <v>18.00522410877839</v>
       </c>
       <c r="D66">
-        <v>36.68391396218194</v>
+        <v>36.51472410877839</v>
       </c>
       <c r="E66">
-        <v>30.51319999999999</v>
+        <v>31.0795</v>
       </c>
       <c r="F66">
-        <v>36.24319999999999</v>
+        <v>36.8095</v>
       </c>
       <c r="G66">
         <v>18.3</v>
@@ -6699,37 +6699,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M66">
-        <v>5.32050176</v>
+        <v>5.4036346</v>
       </c>
       <c r="N66">
-        <v>-0.8355017600000005</v>
+        <v>-0.9186346000000007</v>
       </c>
       <c r="O66">
-        <v>-0.2422955104000001</v>
+        <v>-0.2664040340000002</v>
       </c>
       <c r="P66">
-        <v>-0.5932062496000003</v>
+        <v>-0.6522305660000005</v>
       </c>
       <c r="Q66">
-        <v>0.3467937503999996</v>
+        <v>0.2877694339999994</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5355408969694175</v>
+        <v>0.5495334940256866</v>
       </c>
       <c r="T66">
-        <v>2.995194360605849</v>
+        <v>3.080771342337445</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2444600262663948</v>
+        <v>0.2406991027853733</v>
       </c>
       <c r="W66">
-        <v>0.1109132681440933</v>
+        <v>0.1114653717111072</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8429656078151545</v>
+        <v>0.8299969061564598</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.26478921452121</v>
+        <v>0.26579921452121</v>
       </c>
       <c r="C67">
-        <v>18.00522410877839</v>
+        <v>17.27128773139346</v>
       </c>
       <c r="D67">
-        <v>36.51472410877839</v>
+        <v>36.34708773139345</v>
       </c>
       <c r="E67">
-        <v>31.0795</v>
+        <v>31.6458</v>
       </c>
       <c r="F67">
-        <v>36.8095</v>
+        <v>37.3758</v>
       </c>
       <c r="G67">
         <v>18.3</v>
@@ -6781,37 +6781,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M67">
-        <v>5.4036346</v>
+        <v>5.48676744</v>
       </c>
       <c r="N67">
-        <v>-0.9186346000000007</v>
+        <v>-1.001767440000001</v>
       </c>
       <c r="O67">
-        <v>-0.2664040340000002</v>
+        <v>-0.2905125576000003</v>
       </c>
       <c r="P67">
-        <v>-0.6522305660000005</v>
+        <v>-0.7112548824000007</v>
       </c>
       <c r="Q67">
-        <v>0.2877694339999994</v>
+        <v>0.2287451175999993</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5495334940256866</v>
+        <v>0.5643491850264422</v>
       </c>
       <c r="T67">
-        <v>3.080771342337445</v>
+        <v>3.171382264170899</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2406991027853733</v>
+        <v>0.2370521466825646</v>
       </c>
       <c r="W67">
-        <v>0.1114653717111072</v>
+        <v>0.1120007448669995</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8299969061564598</v>
+        <v>0.8174211954571196</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.26579921452121</v>
+        <v>0.26680921452121</v>
       </c>
       <c r="C68">
-        <v>17.27128773139346</v>
+        <v>16.53888353212631</v>
       </c>
       <c r="D68">
-        <v>36.34708773139345</v>
+        <v>36.18098353212631</v>
       </c>
       <c r="E68">
-        <v>31.6458</v>
+        <v>32.21209999999999</v>
       </c>
       <c r="F68">
-        <v>37.3758</v>
+        <v>37.9421</v>
       </c>
       <c r="G68">
         <v>18.3</v>
@@ -6863,37 +6863,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M68">
-        <v>5.48676744</v>
+        <v>5.56990028</v>
       </c>
       <c r="N68">
-        <v>-1.001767440000001</v>
+        <v>-1.08490028</v>
       </c>
       <c r="O68">
-        <v>-0.2905125576000003</v>
+        <v>-0.3146210812</v>
       </c>
       <c r="P68">
-        <v>-0.7112548824000007</v>
+        <v>-0.7702791988000002</v>
       </c>
       <c r="Q68">
-        <v>0.2287451175999993</v>
+        <v>0.1697208011999998</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5643491850264422</v>
+        <v>0.5800627966939099</v>
       </c>
       <c r="T68">
-        <v>3.171382264170899</v>
+        <v>3.267484757024562</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2370521466825646</v>
+        <v>0.2335140549410339</v>
       </c>
       <c r="W68">
-        <v>0.1120007448669995</v>
+        <v>0.1125201367346562</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8174211954571196</v>
+        <v>0.8052208791070133</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.26680921452121</v>
+        <v>0.3133330471740363</v>
       </c>
       <c r="C69">
-        <v>16.53888353212631</v>
+        <v>9.68073270904538</v>
       </c>
       <c r="D69">
-        <v>36.18098353212631</v>
+        <v>29.88913270904538</v>
       </c>
       <c r="E69">
-        <v>32.21209999999999</v>
+        <v>32.7784</v>
       </c>
       <c r="F69">
-        <v>37.9421</v>
+        <v>38.5084</v>
       </c>
       <c r="G69">
         <v>18.3</v>
@@ -6945,45 +6945,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M69">
-        <v>5.56990028</v>
+        <v>7.732486720000001</v>
       </c>
       <c r="N69">
-        <v>-1.08490028</v>
+        <v>-3.247486720000001</v>
       </c>
       <c r="O69">
-        <v>-0.3146210812</v>
+        <v>-0.9417711488000003</v>
       </c>
       <c r="P69">
-        <v>-0.7702791988000002</v>
+        <v>-2.305715571200001</v>
       </c>
       <c r="Q69">
-        <v>0.1697208011999998</v>
+        <v>-1.365715571200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5800627966939099</v>
+        <v>0.624239236130677</v>
       </c>
       <c r="T69">
-        <v>3.267484757024562</v>
+        <v>3.537662361328075</v>
       </c>
       <c r="U69">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.2335140549410339</v>
+        <v>0.1682059144874936</v>
       </c>
       <c r="W69">
-        <v>0.1125201367346562</v>
+        <v>0.1670242523709113</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8052208791070133</v>
+        <v>0.5800203947844607</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3133330471740363</v>
+        <v>0.3148830471740363</v>
       </c>
       <c r="C70">
-        <v>9.68073270904538</v>
+        <v>8.942262235336358</v>
       </c>
       <c r="D70">
-        <v>29.88913270904538</v>
+        <v>29.71696223533636</v>
       </c>
       <c r="E70">
-        <v>32.7784</v>
+        <v>33.3447</v>
       </c>
       <c r="F70">
-        <v>38.5084</v>
+        <v>39.0747</v>
       </c>
       <c r="G70">
         <v>18.3</v>
@@ -7027,37 +7027,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M70">
-        <v>7.732486720000001</v>
+        <v>7.84619976</v>
       </c>
       <c r="N70">
-        <v>-3.247486720000001</v>
+        <v>-3.361199760000001</v>
       </c>
       <c r="O70">
-        <v>-0.9417711488000003</v>
+        <v>-0.9747479304000002</v>
       </c>
       <c r="P70">
-        <v>-2.305715571200001</v>
+        <v>-2.3864518296</v>
       </c>
       <c r="Q70">
-        <v>-1.365715571200001</v>
+        <v>-1.4464518296</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.624239236130677</v>
+        <v>0.6428985663284408</v>
       </c>
       <c r="T70">
-        <v>3.537662361328075</v>
+        <v>3.651780502016077</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1682059144874936</v>
+        <v>0.1657681476108633</v>
       </c>
       <c r="W70">
-        <v>0.1670242523709113</v>
+        <v>0.1675137559597387</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5800203947844607</v>
+        <v>0.5716143021064251</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3148830471740363</v>
+        <v>0.3164330471740363</v>
       </c>
       <c r="C71">
-        <v>8.942262235336358</v>
+        <v>8.205763909796495</v>
       </c>
       <c r="D71">
-        <v>29.71696223533636</v>
+        <v>29.5467639097965</v>
       </c>
       <c r="E71">
-        <v>33.3447</v>
+        <v>33.911</v>
       </c>
       <c r="F71">
-        <v>39.0747</v>
+        <v>39.641</v>
       </c>
       <c r="G71">
         <v>18.3</v>
@@ -7109,37 +7109,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M71">
-        <v>7.84619976</v>
+        <v>7.9599128</v>
       </c>
       <c r="N71">
-        <v>-3.361199760000001</v>
+        <v>-3.4749128</v>
       </c>
       <c r="O71">
-        <v>-0.9747479304000002</v>
+        <v>-1.007724712</v>
       </c>
       <c r="P71">
-        <v>-2.3864518296</v>
+        <v>-2.467188088</v>
       </c>
       <c r="Q71">
-        <v>-1.4464518296</v>
+        <v>-1.527188088</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6428985663284408</v>
+        <v>0.6628018518727221</v>
       </c>
       <c r="T71">
-        <v>3.651780502016077</v>
+        <v>3.773506518749946</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1657681476108633</v>
+        <v>0.1634000312164224</v>
       </c>
       <c r="W71">
-        <v>0.1675137559597387</v>
+        <v>0.1679892737317424</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5716143021064251</v>
+        <v>0.5634483835049047</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3164330471740363</v>
+        <v>0.3179830471740364</v>
       </c>
       <c r="C72">
-        <v>8.205763909796495</v>
+        <v>7.47120404006661</v>
       </c>
       <c r="D72">
-        <v>29.5467639097965</v>
+        <v>29.37850404006661</v>
       </c>
       <c r="E72">
-        <v>33.911</v>
+        <v>34.4773</v>
       </c>
       <c r="F72">
-        <v>39.641</v>
+        <v>40.2073</v>
       </c>
       <c r="G72">
         <v>18.3</v>
@@ -7191,37 +7191,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M72">
-        <v>7.9599128</v>
+        <v>8.073625840000002</v>
       </c>
       <c r="N72">
-        <v>-3.4749128</v>
+        <v>-3.588625840000002</v>
       </c>
       <c r="O72">
-        <v>-1.007724712</v>
+        <v>-1.040701493600001</v>
       </c>
       <c r="P72">
-        <v>-2.467188088</v>
+        <v>-2.547924346400002</v>
       </c>
       <c r="Q72">
-        <v>-1.527188088</v>
+        <v>-1.607924346400002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6628018518727221</v>
+        <v>0.6840777777993678</v>
       </c>
       <c r="T72">
-        <v>3.773506518749946</v>
+        <v>3.9036274331896</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1634000312164224</v>
+        <v>0.1610986223260502</v>
       </c>
       <c r="W72">
-        <v>0.1679892737317424</v>
+        <v>0.1684513966369291</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5634483835049047</v>
+        <v>0.5555124907794833</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3179830471740362</v>
+        <v>0.3195330471740362</v>
       </c>
       <c r="C73">
-        <v>7.471204040066631</v>
+        <v>6.738549696912905</v>
       </c>
       <c r="D73">
-        <v>29.37850404006662</v>
+        <v>29.2121496969129</v>
       </c>
       <c r="E73">
-        <v>34.4773</v>
+        <v>35.0436</v>
       </c>
       <c r="F73">
-        <v>40.2073</v>
+        <v>40.77359999999999</v>
       </c>
       <c r="G73">
         <v>18.3</v>
@@ -7273,37 +7273,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M73">
-        <v>8.07362584</v>
+        <v>8.187338879999999</v>
       </c>
       <c r="N73">
-        <v>-3.588625840000001</v>
+        <v>-3.702338879999999</v>
       </c>
       <c r="O73">
-        <v>-1.0407014936</v>
+        <v>-1.0736782752</v>
       </c>
       <c r="P73">
-        <v>-2.5479243464</v>
+        <v>-2.628660604799999</v>
       </c>
       <c r="Q73">
-        <v>-1.6079243464</v>
+        <v>-1.688660604799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6840777777993675</v>
+        <v>0.7068734127207735</v>
       </c>
       <c r="T73">
-        <v>3.903627433189598</v>
+        <v>4.043042698660655</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1610986223260502</v>
+        <v>0.1588611414604106</v>
       </c>
       <c r="W73">
-        <v>0.1684513966369291</v>
+        <v>0.1689006827947495</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5555124907794835</v>
+        <v>0.5477970395186573</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3195330471740362</v>
+        <v>0.3210830471740363</v>
       </c>
       <c r="C74">
-        <v>6.738549696912905</v>
+        <v>6.007768692742715</v>
       </c>
       <c r="D74">
-        <v>29.2121496969129</v>
+        <v>29.04766869274271</v>
       </c>
       <c r="E74">
-        <v>35.0436</v>
+        <v>35.6099</v>
       </c>
       <c r="F74">
-        <v>40.77359999999999</v>
+        <v>41.33989999999999</v>
       </c>
       <c r="G74">
         <v>18.3</v>
@@ -7355,37 +7355,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M74">
-        <v>8.187338879999999</v>
+        <v>8.301051919999999</v>
       </c>
       <c r="N74">
-        <v>-3.702338879999999</v>
+        <v>-3.81605192</v>
       </c>
       <c r="O74">
-        <v>-1.0736782752</v>
+        <v>-1.1066550568</v>
       </c>
       <c r="P74">
-        <v>-2.628660604799999</v>
+        <v>-2.7093968632</v>
       </c>
       <c r="Q74">
-        <v>-1.688660604799999</v>
+        <v>-1.7693968632</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.7068734127207735</v>
+        <v>0.7313576131919134</v>
       </c>
       <c r="T74">
-        <v>4.043042698660655</v>
+        <v>4.192785020833273</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1588611414604106</v>
+        <v>0.156684961440405</v>
       </c>
       <c r="W74">
-        <v>0.1689006827947495</v>
+        <v>0.1693376597427667</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5477970395186573</v>
+        <v>0.5402929704841553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3210830471740363</v>
+        <v>0.3226330471740363</v>
       </c>
       <c r="C75">
-        <v>6.007768692742715</v>
+        <v>5.278829560842226</v>
       </c>
       <c r="D75">
-        <v>29.04766869274271</v>
+        <v>28.88502956084222</v>
       </c>
       <c r="E75">
-        <v>35.6099</v>
+        <v>36.17619999999999</v>
       </c>
       <c r="F75">
-        <v>41.33989999999999</v>
+        <v>41.9062</v>
       </c>
       <c r="G75">
         <v>18.3</v>
@@ -7437,37 +7437,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M75">
-        <v>8.301051919999999</v>
+        <v>8.414764959999999</v>
       </c>
       <c r="N75">
-        <v>-3.81605192</v>
+        <v>-3.92976496</v>
       </c>
       <c r="O75">
-        <v>-1.1066550568</v>
+        <v>-1.1396318384</v>
       </c>
       <c r="P75">
-        <v>-2.7093968632</v>
+        <v>-2.7901331216</v>
       </c>
       <c r="Q75">
-        <v>-1.7693968632</v>
+        <v>-1.8501331216</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.7313576131919134</v>
+        <v>0.7577252136992946</v>
       </c>
       <c r="T75">
-        <v>4.192785020833273</v>
+        <v>4.354045983173013</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.156684961440405</v>
+        <v>0.1545675970966157</v>
       </c>
       <c r="W75">
-        <v>0.1693376597427667</v>
+        <v>0.1697628265029996</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5402929704841553</v>
+        <v>0.5329917141262612</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3226330471740363</v>
+        <v>0.3241830471740362</v>
       </c>
       <c r="C76">
-        <v>5.278829560842226</v>
+        <v>4.551701535307636</v>
       </c>
       <c r="D76">
-        <v>28.88502956084222</v>
+        <v>28.72420153530763</v>
       </c>
       <c r="E76">
-        <v>36.17619999999999</v>
+        <v>36.74249999999999</v>
       </c>
       <c r="F76">
-        <v>41.9062</v>
+        <v>42.4725</v>
       </c>
       <c r="G76">
         <v>18.3</v>
@@ -7519,37 +7519,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M76">
-        <v>8.414764959999999</v>
+        <v>8.528478</v>
       </c>
       <c r="N76">
-        <v>-3.92976496</v>
+        <v>-4.043478</v>
       </c>
       <c r="O76">
-        <v>-1.1396318384</v>
+        <v>-1.17260862</v>
       </c>
       <c r="P76">
-        <v>-2.7901331216</v>
+        <v>-2.87086938</v>
       </c>
       <c r="Q76">
-        <v>-1.8501331216</v>
+        <v>-1.93086938</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7577252136992946</v>
+        <v>0.7862022222472663</v>
       </c>
       <c r="T76">
-        <v>4.354045983173013</v>
+        <v>4.528207822499934</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1545675970966157</v>
+        <v>0.1525066958019942</v>
       </c>
       <c r="W76">
-        <v>0.1697628265029996</v>
+        <v>0.1701766554829596</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5329917141262612</v>
+        <v>0.525885157937911</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3241830471740362</v>
+        <v>0.3257330471740363</v>
       </c>
       <c r="C77">
-        <v>4.551701535307636</v>
+        <v>3.826354531643048</v>
       </c>
       <c r="D77">
-        <v>28.72420153530763</v>
+        <v>28.56515453164304</v>
       </c>
       <c r="E77">
-        <v>36.74249999999999</v>
+        <v>37.30879999999999</v>
       </c>
       <c r="F77">
-        <v>42.4725</v>
+        <v>43.03879999999999</v>
       </c>
       <c r="G77">
         <v>18.3</v>
@@ -7601,37 +7601,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M77">
-        <v>8.528478</v>
+        <v>8.642191039999998</v>
       </c>
       <c r="N77">
-        <v>-4.043478</v>
+        <v>-4.157191039999999</v>
       </c>
       <c r="O77">
-        <v>-1.17260862</v>
+        <v>-1.2055854016</v>
       </c>
       <c r="P77">
-        <v>-2.87086938</v>
+        <v>-2.951605638399999</v>
       </c>
       <c r="Q77">
-        <v>-1.93086938</v>
+        <v>-2.011605638399999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7862022222472663</v>
+        <v>0.8170523148409025</v>
       </c>
       <c r="T77">
-        <v>4.528207822499934</v>
+        <v>4.716883148437431</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1525066958019942</v>
+        <v>0.150500028751968</v>
       </c>
       <c r="W77">
-        <v>0.1701766554829596</v>
+        <v>0.1705795942266048</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.525885157937911</v>
+        <v>0.5189656163860965</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3257330471740363</v>
+        <v>0.3272830471740363</v>
       </c>
       <c r="C78">
-        <v>3.826354531643048</v>
+        <v>3.102759127999526</v>
       </c>
       <c r="D78">
-        <v>28.56515453164304</v>
+        <v>28.40785912799953</v>
       </c>
       <c r="E78">
-        <v>37.30879999999999</v>
+        <v>37.8751</v>
       </c>
       <c r="F78">
-        <v>43.03879999999999</v>
+        <v>43.6051</v>
       </c>
       <c r="G78">
         <v>18.3</v>
@@ -7683,37 +7683,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M78">
-        <v>8.642191039999998</v>
+        <v>8.755904080000001</v>
       </c>
       <c r="N78">
-        <v>-4.157191039999999</v>
+        <v>-4.270904080000001</v>
       </c>
       <c r="O78">
-        <v>-1.2055854016</v>
+        <v>-1.2385621832</v>
       </c>
       <c r="P78">
-        <v>-2.951605638399999</v>
+        <v>-3.032341896800001</v>
       </c>
       <c r="Q78">
-        <v>-2.011605638399999</v>
+        <v>-2.092341896800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.8170523148409025</v>
+        <v>0.8505850241818115</v>
       </c>
       <c r="T78">
-        <v>4.716883148437431</v>
+        <v>4.921965024456451</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.150500028751968</v>
+        <v>0.1485454829240203</v>
       </c>
       <c r="W78">
-        <v>0.1705795942266048</v>
+        <v>0.1709720670288567</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5189656163860965</v>
+        <v>0.512225803186277</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3272830471740363</v>
+        <v>0.3288330471740363</v>
       </c>
       <c r="C79">
-        <v>3.102759127999526</v>
+        <v>2.380886547030485</v>
       </c>
       <c r="D79">
-        <v>28.40785912799953</v>
+        <v>28.25228654703048</v>
       </c>
       <c r="E79">
-        <v>37.8751</v>
+        <v>38.4414</v>
       </c>
       <c r="F79">
-        <v>43.6051</v>
+        <v>44.1714</v>
       </c>
       <c r="G79">
         <v>18.3</v>
@@ -7765,37 +7765,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M79">
-        <v>8.755904080000001</v>
+        <v>8.869617119999999</v>
       </c>
       <c r="N79">
-        <v>-4.270904080000001</v>
+        <v>-4.38461712</v>
       </c>
       <c r="O79">
-        <v>-1.2385621832</v>
+        <v>-1.2715389648</v>
       </c>
       <c r="P79">
-        <v>-3.032341896800001</v>
+        <v>-3.1130781552</v>
       </c>
       <c r="Q79">
-        <v>-2.092341896800001</v>
+        <v>-2.1730781552</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8505850241818115</v>
+        <v>0.8871661616446209</v>
       </c>
       <c r="T79">
-        <v>4.921965024456451</v>
+        <v>5.145690707386289</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1485454829240203</v>
+        <v>0.1466410536557637</v>
       </c>
       <c r="W79">
-        <v>0.1709720670288567</v>
+        <v>0.1713544764259227</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.512225803186277</v>
+        <v>0.5056588057095299</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3288330471740363</v>
+        <v>0.3615814648671709</v>
       </c>
       <c r="C80">
-        <v>2.380886547030485</v>
+        <v>-1.115343748332045</v>
       </c>
       <c r="D80">
-        <v>28.25228654703048</v>
+        <v>25.32235625166795</v>
       </c>
       <c r="E80">
-        <v>38.4414</v>
+        <v>39.0077</v>
       </c>
       <c r="F80">
-        <v>44.1714</v>
+        <v>44.7377</v>
       </c>
       <c r="G80">
         <v>18.3</v>
@@ -7847,45 +7847,45 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M80">
-        <v>8.869617119999999</v>
+        <v>10.54914966</v>
       </c>
       <c r="N80">
-        <v>-4.38461712</v>
+        <v>-6.06414966</v>
       </c>
       <c r="O80">
-        <v>-1.2715389648</v>
+        <v>-1.7586034014</v>
       </c>
       <c r="P80">
-        <v>-3.1130781552</v>
+        <v>-4.3055462586</v>
       </c>
       <c r="Q80">
-        <v>-2.1730781552</v>
+        <v>-3.3655462586</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8871661616446209</v>
+        <v>0.9441284440711964</v>
       </c>
       <c r="T80">
-        <v>5.145690707386289</v>
+        <v>5.494064935773368</v>
       </c>
       <c r="U80">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1466410536557637</v>
+        <v>0.1232942978268449</v>
       </c>
       <c r="W80">
-        <v>0.1713544764259227</v>
+        <v>0.20672720457243</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5056588057095299</v>
+        <v>0.4251527511270514</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3615814648671709</v>
+        <v>0.3634814648671709</v>
       </c>
       <c r="C81">
-        <v>-1.115343748332045</v>
+        <v>-1.833092549093173</v>
       </c>
       <c r="D81">
-        <v>25.32235625166795</v>
+        <v>25.17090745090683</v>
       </c>
       <c r="E81">
-        <v>39.0077</v>
+        <v>39.574</v>
       </c>
       <c r="F81">
-        <v>44.7377</v>
+        <v>45.304</v>
       </c>
       <c r="G81">
         <v>18.3</v>
@@ -7929,37 +7929,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M81">
-        <v>10.54914966</v>
+        <v>10.6826832</v>
       </c>
       <c r="N81">
-        <v>-6.06414966</v>
+        <v>-6.197683200000002</v>
       </c>
       <c r="O81">
-        <v>-1.7586034014</v>
+        <v>-1.797328128</v>
       </c>
       <c r="P81">
-        <v>-4.3055462586</v>
+        <v>-4.400355072000002</v>
       </c>
       <c r="Q81">
-        <v>-3.3655462586</v>
+        <v>-3.460355072000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.9441284440711964</v>
+        <v>0.9890448662747563</v>
       </c>
       <c r="T81">
-        <v>5.494064935773368</v>
+        <v>5.768768182562036</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1232942978268449</v>
+        <v>0.1217531191040093</v>
       </c>
       <c r="W81">
-        <v>0.20672720457243</v>
+        <v>0.2070906145152746</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4251527511270514</v>
+        <v>0.4198383417379633</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3634814648671709</v>
+        <v>0.3653814648671709</v>
       </c>
       <c r="C82">
-        <v>-1.833092549093173</v>
+        <v>-2.549040540025942</v>
       </c>
       <c r="D82">
-        <v>25.17090745090683</v>
+        <v>25.02125945997406</v>
       </c>
       <c r="E82">
-        <v>39.574</v>
+        <v>40.1403</v>
       </c>
       <c r="F82">
-        <v>45.304</v>
+        <v>45.8703</v>
       </c>
       <c r="G82">
         <v>18.3</v>
@@ -8011,37 +8011,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M82">
-        <v>10.6826832</v>
+        <v>10.81621674</v>
       </c>
       <c r="N82">
-        <v>-6.197683200000002</v>
+        <v>-6.33121674</v>
       </c>
       <c r="O82">
-        <v>-1.797328128</v>
+        <v>-1.8360528546</v>
       </c>
       <c r="P82">
-        <v>-4.400355072000002</v>
+        <v>-4.4951638854</v>
       </c>
       <c r="Q82">
-        <v>-3.460355072000002</v>
+        <v>-3.5551638854</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.9890448662747563</v>
+        <v>1.038689332920796</v>
       </c>
       <c r="T82">
-        <v>5.768768182562036</v>
+        <v>6.072387560591618</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1217531191040093</v>
+        <v>0.1202499941767994</v>
       </c>
       <c r="W82">
-        <v>0.2070906145152746</v>
+        <v>0.2074450513731107</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4198383417379633</v>
+        <v>0.4146551523337909</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3653814648671709</v>
+        <v>0.3672814648671709</v>
       </c>
       <c r="C83">
-        <v>-2.549040540025942</v>
+        <v>-3.26321965023714</v>
       </c>
       <c r="D83">
-        <v>25.02125945997406</v>
+        <v>24.87338034976286</v>
       </c>
       <c r="E83">
-        <v>40.1403</v>
+        <v>40.70659999999999</v>
       </c>
       <c r="F83">
-        <v>45.8703</v>
+        <v>46.4366</v>
       </c>
       <c r="G83">
         <v>18.3</v>
@@ -8093,37 +8093,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M83">
-        <v>10.81621674</v>
+        <v>10.94975028</v>
       </c>
       <c r="N83">
-        <v>-6.33121674</v>
+        <v>-6.464750280000001</v>
       </c>
       <c r="O83">
-        <v>-1.8360528546</v>
+        <v>-1.8747775812</v>
       </c>
       <c r="P83">
-        <v>-4.4951638854</v>
+        <v>-4.5899726988</v>
       </c>
       <c r="Q83">
-        <v>-3.5551638854</v>
+        <v>-3.649972698800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>1.038689332920796</v>
+        <v>1.093849851416396</v>
       </c>
       <c r="T83">
-        <v>6.072387560591618</v>
+        <v>6.40974242506893</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1202499941767994</v>
+        <v>0.1187835308331799</v>
       </c>
       <c r="W83">
-        <v>0.2074450513731107</v>
+        <v>0.2077908434295362</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4146551523337909</v>
+        <v>0.4095983821833789</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3672814648671709</v>
+        <v>0.3691814648671708</v>
       </c>
       <c r="C84">
-        <v>-3.26321965023714</v>
+        <v>-3.975661058446661</v>
       </c>
       <c r="D84">
-        <v>24.87338034976286</v>
+        <v>24.72723894155333</v>
       </c>
       <c r="E84">
-        <v>40.70659999999999</v>
+        <v>41.27289999999999</v>
       </c>
       <c r="F84">
-        <v>46.4366</v>
+        <v>47.0029</v>
       </c>
       <c r="G84">
         <v>18.3</v>
@@ -8175,37 +8175,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M84">
-        <v>10.94975028</v>
+        <v>11.08328382</v>
       </c>
       <c r="N84">
-        <v>-6.464750280000001</v>
+        <v>-6.598283820000001</v>
       </c>
       <c r="O84">
-        <v>-1.8747775812</v>
+        <v>-1.9135023078</v>
       </c>
       <c r="P84">
-        <v>-4.5899726988</v>
+        <v>-4.684781512200001</v>
       </c>
       <c r="Q84">
-        <v>-3.649972698800001</v>
+        <v>-3.744781512200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.093849851416396</v>
+        <v>1.155499842676184</v>
       </c>
       <c r="T84">
-        <v>6.40974242506893</v>
+        <v>6.786786097131808</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1187835308331799</v>
+        <v>0.1173524039556717</v>
       </c>
       <c r="W84">
-        <v>0.2077908434295362</v>
+        <v>0.2081283031472526</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4095983821833789</v>
+        <v>0.4046634619161092</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3691814648671708</v>
+        <v>0.371081464867171</v>
       </c>
       <c r="C85">
-        <v>-3.975661058446661</v>
+        <v>-4.686395214902952</v>
       </c>
       <c r="D85">
-        <v>24.72723894155333</v>
+        <v>24.58280478509705</v>
       </c>
       <c r="E85">
-        <v>41.27289999999999</v>
+        <v>41.83920000000001</v>
       </c>
       <c r="F85">
-        <v>47.0029</v>
+        <v>47.5692</v>
       </c>
       <c r="G85">
         <v>18.3</v>
@@ -8257,37 +8257,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M85">
-        <v>11.08328382</v>
+        <v>11.21681736</v>
       </c>
       <c r="N85">
-        <v>-6.598283820000001</v>
+        <v>-6.731817360000001</v>
       </c>
       <c r="O85">
-        <v>-1.9135023078</v>
+        <v>-1.9522270344</v>
       </c>
       <c r="P85">
-        <v>-4.684781512200001</v>
+        <v>-4.779590325600001</v>
       </c>
       <c r="Q85">
-        <v>-3.744781512200001</v>
+        <v>-3.839590325600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.155499842676184</v>
+        <v>1.224856082843446</v>
       </c>
       <c r="T85">
-        <v>6.786786097131808</v>
+        <v>7.210960228202548</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1173524039556717</v>
+        <v>0.115955351527628</v>
       </c>
       <c r="W85">
-        <v>0.2081283031472526</v>
+        <v>0.2084577281097854</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4046634619161092</v>
+        <v>0.3998460397504412</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.371081464867171</v>
+        <v>0.3729814648671709</v>
       </c>
       <c r="C86">
-        <v>-4.686395214902944</v>
+        <v>-5.395451862534692</v>
       </c>
       <c r="D86">
-        <v>24.58280478509705</v>
+        <v>24.4400481374653</v>
       </c>
       <c r="E86">
-        <v>41.83919999999999</v>
+        <v>42.40549999999999</v>
       </c>
       <c r="F86">
-        <v>47.5692</v>
+        <v>48.13549999999999</v>
       </c>
       <c r="G86">
         <v>18.3</v>
@@ -8339,37 +8339,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M86">
-        <v>11.21681736</v>
+        <v>11.3503509</v>
       </c>
       <c r="N86">
-        <v>-6.731817359999999</v>
+        <v>-6.865350899999999</v>
       </c>
       <c r="O86">
-        <v>-1.9522270344</v>
+        <v>-1.990951761</v>
       </c>
       <c r="P86">
-        <v>-4.779590325599999</v>
+        <v>-4.874399138999999</v>
       </c>
       <c r="Q86">
-        <v>-3.839590325599999</v>
+        <v>-3.934399138999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.224856082843445</v>
+        <v>1.303459821699675</v>
       </c>
       <c r="T86">
-        <v>7.210960228202543</v>
+        <v>7.691690910082713</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.115955351527628</v>
+        <v>0.1145911709214206</v>
       </c>
       <c r="W86">
-        <v>0.2084577281097854</v>
+        <v>0.208779401896729</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3998460397504413</v>
+        <v>0.3951419686945538</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3729814648671709</v>
+        <v>0.3748814648671709</v>
       </c>
       <c r="C87">
-        <v>-5.395451862534692</v>
+        <v>-6.102860057370059</v>
       </c>
       <c r="D87">
-        <v>24.4400481374653</v>
+        <v>24.29893994262994</v>
       </c>
       <c r="E87">
-        <v>42.40549999999999</v>
+        <v>42.9718</v>
       </c>
       <c r="F87">
-        <v>48.13549999999999</v>
+        <v>48.7018</v>
       </c>
       <c r="G87">
         <v>18.3</v>
@@ -8421,37 +8421,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M87">
-        <v>11.3503509</v>
+        <v>11.48388444</v>
       </c>
       <c r="N87">
-        <v>-6.865350899999999</v>
+        <v>-6.998884440000001</v>
       </c>
       <c r="O87">
-        <v>-1.990951761</v>
+        <v>-2.0296764876</v>
       </c>
       <c r="P87">
-        <v>-4.874399138999999</v>
+        <v>-4.969207952400001</v>
       </c>
       <c r="Q87">
-        <v>-3.934399138999999</v>
+        <v>-4.029207952400002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.303459821699675</v>
+        <v>1.393292666106794</v>
       </c>
       <c r="T87">
-        <v>7.691690910082713</v>
+        <v>8.241097403660049</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1145911709214206</v>
+        <v>0.1132587154455901</v>
       </c>
       <c r="W87">
-        <v>0.208779401896729</v>
+        <v>0.2090935948979299</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3951419686945538</v>
+        <v>0.3905472946399658</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3748814648671709</v>
+        <v>0.3767814648671709</v>
       </c>
       <c r="C88">
-        <v>-6.102860057370059</v>
+        <v>-6.808648188252327</v>
       </c>
       <c r="D88">
-        <v>24.29893994262994</v>
+        <v>24.15945181174767</v>
       </c>
       <c r="E88">
-        <v>42.9718</v>
+        <v>43.5381</v>
       </c>
       <c r="F88">
-        <v>48.7018</v>
+        <v>49.2681</v>
       </c>
       <c r="G88">
         <v>18.3</v>
@@ -8503,37 +8503,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M88">
-        <v>11.48388444</v>
+        <v>11.61741798</v>
       </c>
       <c r="N88">
-        <v>-6.998884440000001</v>
+        <v>-7.13241798</v>
       </c>
       <c r="O88">
-        <v>-2.0296764876</v>
+        <v>-2.0684012142</v>
       </c>
       <c r="P88">
-        <v>-4.969207952400001</v>
+        <v>-5.0640167658</v>
       </c>
       <c r="Q88">
-        <v>-4.029207952400002</v>
+        <v>-4.1240167658</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.393292666106794</v>
+        <v>1.49694594811501</v>
       </c>
       <c r="T88">
-        <v>8.241097403660049</v>
+        <v>8.875027973172362</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1132587154455901</v>
+        <v>0.1119568911301236</v>
       </c>
       <c r="W88">
-        <v>0.2090935948979299</v>
+        <v>0.2094005650715169</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3905472946399658</v>
+        <v>0.3860582452762882</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3767814648671709</v>
+        <v>0.3786814648671709</v>
       </c>
       <c r="C89">
-        <v>-6.808648188252327</v>
+        <v>-7.512843995880537</v>
       </c>
       <c r="D89">
-        <v>24.15945181174767</v>
+        <v>24.02155600411945</v>
       </c>
       <c r="E89">
-        <v>43.5381</v>
+        <v>44.1044</v>
       </c>
       <c r="F89">
-        <v>49.2681</v>
+        <v>49.8344</v>
       </c>
       <c r="G89">
         <v>18.3</v>
@@ -8585,37 +8585,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M89">
-        <v>11.61741798</v>
+        <v>11.75095152</v>
       </c>
       <c r="N89">
-        <v>-7.13241798</v>
+        <v>-7.26595152</v>
       </c>
       <c r="O89">
-        <v>-2.0684012142</v>
+        <v>-2.1071259408</v>
       </c>
       <c r="P89">
-        <v>-5.0640167658</v>
+        <v>-5.1588255792</v>
       </c>
       <c r="Q89">
-        <v>-4.1240167658</v>
+        <v>-4.218825579200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.49694594811501</v>
+        <v>1.617874777124593</v>
       </c>
       <c r="T89">
-        <v>8.875027973172362</v>
+        <v>9.614613637603391</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1119568911301236</v>
+        <v>0.1106846537309176</v>
       </c>
       <c r="W89">
-        <v>0.2094005650715169</v>
+        <v>0.2097005586502496</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3860582452762882</v>
+        <v>0.3816712197617849</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3786814648671709</v>
+        <v>0.3805814648671709</v>
       </c>
       <c r="C90">
-        <v>-7.512843995880537</v>
+        <v>-8.215474591201691</v>
       </c>
       <c r="D90">
-        <v>24.02155600411945</v>
+        <v>23.88522540879831</v>
       </c>
       <c r="E90">
-        <v>44.1044</v>
+        <v>44.6707</v>
       </c>
       <c r="F90">
-        <v>49.8344</v>
+        <v>50.40069999999999</v>
       </c>
       <c r="G90">
         <v>18.3</v>
@@ -8667,37 +8667,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M90">
-        <v>11.75095152</v>
+        <v>11.88448506</v>
       </c>
       <c r="N90">
-        <v>-7.26595152</v>
+        <v>-7.39948506</v>
       </c>
       <c r="O90">
-        <v>-2.1071259408</v>
+        <v>-2.1458506674</v>
       </c>
       <c r="P90">
-        <v>-5.1588255792</v>
+        <v>-5.2536343926</v>
       </c>
       <c r="Q90">
-        <v>-4.218825579200001</v>
+        <v>-4.313634392600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.617874777124593</v>
+        <v>1.760790665954102</v>
       </c>
       <c r="T90">
-        <v>9.614613637603391</v>
+        <v>10.48866942284006</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1106846537309176</v>
+        <v>0.1094410059361882</v>
       </c>
       <c r="W90">
-        <v>0.2097005586502496</v>
+        <v>0.2099938108002468</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3816712197617849</v>
+        <v>0.3773827790903042</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3805814648671709</v>
+        <v>0.3824814648671709</v>
       </c>
       <c r="C91">
-        <v>-8.215474591201691</v>
+        <v>-8.916566473180168</v>
       </c>
       <c r="D91">
-        <v>23.88522540879831</v>
+        <v>23.75043352681983</v>
       </c>
       <c r="E91">
-        <v>44.6707</v>
+        <v>45.23699999999999</v>
       </c>
       <c r="F91">
-        <v>50.40069999999999</v>
+        <v>50.967</v>
       </c>
       <c r="G91">
         <v>18.3</v>
@@ -8749,37 +8749,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M91">
-        <v>11.88448506</v>
+        <v>12.0180186</v>
       </c>
       <c r="N91">
-        <v>-7.39948506</v>
+        <v>-7.5330186</v>
       </c>
       <c r="O91">
-        <v>-2.1458506674</v>
+        <v>-2.184575394</v>
       </c>
       <c r="P91">
-        <v>-5.2536343926</v>
+        <v>-5.348443206000001</v>
       </c>
       <c r="Q91">
-        <v>-4.313634392600001</v>
+        <v>-4.408443206000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.760790665954102</v>
+        <v>1.932289732549513</v>
       </c>
       <c r="T91">
-        <v>10.48866942284006</v>
+        <v>11.53753636512407</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1094410059361882</v>
+        <v>0.1082249947591194</v>
       </c>
       <c r="W91">
-        <v>0.2099938108002468</v>
+        <v>0.2102805462357996</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3773827790903042</v>
+        <v>0.3731896371004119</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3824814648671709</v>
+        <v>0.384381464867171</v>
       </c>
       <c r="C92">
-        <v>-8.916566473180168</v>
+        <v>-9.616145545968934</v>
       </c>
       <c r="D92">
-        <v>23.75043352681983</v>
+        <v>23.61715445403106</v>
       </c>
       <c r="E92">
-        <v>45.23699999999999</v>
+        <v>45.80329999999999</v>
       </c>
       <c r="F92">
-        <v>50.967</v>
+        <v>51.5333</v>
       </c>
       <c r="G92">
         <v>18.3</v>
@@ -8831,37 +8831,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M92">
-        <v>12.0180186</v>
+        <v>12.15155214</v>
       </c>
       <c r="N92">
-        <v>-7.5330186</v>
+        <v>-7.66655214</v>
       </c>
       <c r="O92">
-        <v>-2.184575394</v>
+        <v>-2.2233001206</v>
       </c>
       <c r="P92">
-        <v>-5.348443206000001</v>
+        <v>-5.443252019400001</v>
       </c>
       <c r="Q92">
-        <v>-4.408443206000001</v>
+        <v>-4.503252019400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.932289732549513</v>
+        <v>2.141899702832792</v>
       </c>
       <c r="T92">
-        <v>11.53753636512407</v>
+        <v>12.81948485013786</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1082249947591194</v>
+        <v>0.1070357091024258</v>
       </c>
       <c r="W92">
-        <v>0.2102805462357996</v>
+        <v>0.210560979793648</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3731896371004119</v>
+        <v>0.3690886520773304</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.384381464867171</v>
+        <v>0.3862814648671709</v>
       </c>
       <c r="C93">
-        <v>-9.616145545968934</v>
+        <v>-10.31423713550572</v>
       </c>
       <c r="D93">
-        <v>23.61715445403106</v>
+        <v>23.48536286449427</v>
       </c>
       <c r="E93">
-        <v>45.80329999999999</v>
+        <v>46.36959999999999</v>
       </c>
       <c r="F93">
-        <v>51.5333</v>
+        <v>52.0996</v>
       </c>
       <c r="G93">
         <v>18.3</v>
@@ -8913,37 +8913,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M93">
-        <v>12.15155214</v>
+        <v>12.28508568</v>
       </c>
       <c r="N93">
-        <v>-7.66655214</v>
+        <v>-7.80008568</v>
       </c>
       <c r="O93">
-        <v>-2.2233001206</v>
+        <v>-2.2620248472</v>
       </c>
       <c r="P93">
-        <v>-5.443252019400001</v>
+        <v>-5.5380608328</v>
       </c>
       <c r="Q93">
-        <v>-4.503252019400001</v>
+        <v>-4.5980608328</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>2.141899702832792</v>
+        <v>2.403912165686891</v>
       </c>
       <c r="T93">
-        <v>12.81948485013786</v>
+        <v>14.4219204564051</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1070357091024258</v>
+        <v>0.1058722774817473</v>
       </c>
       <c r="W93">
-        <v>0.210560979793648</v>
+        <v>0.210835316969804</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3690886520773304</v>
+        <v>0.3650768189025768</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3862814648671709</v>
+        <v>0.3881814648671709</v>
       </c>
       <c r="C94">
-        <v>-10.31423713550572</v>
+        <v>-11.01086600555671</v>
       </c>
       <c r="D94">
-        <v>23.48536286449427</v>
+        <v>23.35503399444329</v>
       </c>
       <c r="E94">
-        <v>46.36959999999999</v>
+        <v>46.9359</v>
       </c>
       <c r="F94">
-        <v>52.0996</v>
+        <v>52.6659</v>
       </c>
       <c r="G94">
         <v>18.3</v>
@@ -8995,37 +8995,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M94">
-        <v>12.28508568</v>
+        <v>12.41861922</v>
       </c>
       <c r="N94">
-        <v>-7.80008568</v>
+        <v>-7.933619220000001</v>
       </c>
       <c r="O94">
-        <v>-2.2620248472</v>
+        <v>-2.3007495738</v>
       </c>
       <c r="P94">
-        <v>-5.5380608328</v>
+        <v>-5.632869646200001</v>
       </c>
       <c r="Q94">
-        <v>-4.5980608328</v>
+        <v>-4.6928696462</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.403912165686891</v>
+        <v>2.74078533221359</v>
       </c>
       <c r="T94">
-        <v>14.4219204564051</v>
+        <v>16.48219480732011</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1058722774817473</v>
+        <v>0.104733865895922</v>
       </c>
       <c r="W94">
-        <v>0.210835316969804</v>
+        <v>0.2111037544217416</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3650768189025768</v>
+        <v>0.3611512617100759</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3881814648671709</v>
+        <v>0.3900814648671709</v>
       </c>
       <c r="C95">
-        <v>-11.01086600555671</v>
+        <v>-11.70605637322888</v>
       </c>
       <c r="D95">
-        <v>23.35503399444329</v>
+        <v>23.22614362677112</v>
       </c>
       <c r="E95">
-        <v>46.9359</v>
+        <v>47.5022</v>
       </c>
       <c r="F95">
-        <v>52.6659</v>
+        <v>53.2322</v>
       </c>
       <c r="G95">
         <v>18.3</v>
@@ -9077,37 +9077,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M95">
-        <v>12.41861922</v>
+        <v>12.55215276</v>
       </c>
       <c r="N95">
-        <v>-7.933619220000001</v>
+        <v>-8.067152760000001</v>
       </c>
       <c r="O95">
-        <v>-2.3007495738</v>
+        <v>-2.3394743004</v>
       </c>
       <c r="P95">
-        <v>-5.632869646200001</v>
+        <v>-5.727678459600001</v>
       </c>
       <c r="Q95">
-        <v>-4.6928696462</v>
+        <v>-4.7876784596</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.74078533221359</v>
+        <v>3.18994955424919</v>
       </c>
       <c r="T95">
-        <v>16.48219480732011</v>
+        <v>19.2292272752068</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.104733865895922</v>
+        <v>0.1036196758331994</v>
       </c>
       <c r="W95">
-        <v>0.2111037544217416</v>
+        <v>0.2113664804385316</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3611512617100759</v>
+        <v>0.3573092270110326</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3900814648671709</v>
+        <v>0.3919814648671709</v>
       </c>
       <c r="C96">
-        <v>-11.70605637322888</v>
+        <v>-12.3998319239716</v>
       </c>
       <c r="D96">
-        <v>23.22614362677112</v>
+        <v>23.0986680760284</v>
       </c>
       <c r="E96">
-        <v>47.5022</v>
+        <v>48.0685</v>
       </c>
       <c r="F96">
-        <v>53.2322</v>
+        <v>53.7985</v>
       </c>
       <c r="G96">
         <v>18.3</v>
@@ -9159,37 +9159,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M96">
-        <v>12.55215276</v>
+        <v>12.6856863</v>
       </c>
       <c r="N96">
-        <v>-8.067152760000001</v>
+        <v>-8.200686300000001</v>
       </c>
       <c r="O96">
-        <v>-2.3394743004</v>
+        <v>-2.378199027</v>
       </c>
       <c r="P96">
-        <v>-5.727678459600001</v>
+        <v>-5.822487273000001</v>
       </c>
       <c r="Q96">
-        <v>-4.7876784596</v>
+        <v>-4.882487273000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>3.18994955424919</v>
+        <v>3.81877946509903</v>
       </c>
       <c r="T96">
-        <v>19.2292272752068</v>
+        <v>23.07507273024817</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1036196758331994</v>
+        <v>0.1025289424033763</v>
       </c>
       <c r="W96">
-        <v>0.2113664804385316</v>
+        <v>0.2116236753812839</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3573092270110326</v>
+        <v>0.3535480772530217</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3919814648671709</v>
+        <v>0.3938814648671709</v>
       </c>
       <c r="C97">
-        <v>-12.3998319239716</v>
+        <v>-13.09221582608687</v>
       </c>
       <c r="D97">
-        <v>23.0986680760284</v>
+        <v>22.97258417391313</v>
       </c>
       <c r="E97">
-        <v>48.0685</v>
+        <v>48.6348</v>
       </c>
       <c r="F97">
-        <v>53.7985</v>
+        <v>54.3648</v>
       </c>
       <c r="G97">
         <v>18.3</v>
@@ -9241,37 +9241,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M97">
-        <v>12.6856863</v>
+        <v>12.81921984</v>
       </c>
       <c r="N97">
-        <v>-8.200686300000001</v>
+        <v>-8.334219840000001</v>
       </c>
       <c r="O97">
-        <v>-2.378199027</v>
+        <v>-2.4169237536</v>
       </c>
       <c r="P97">
-        <v>-5.822487273000001</v>
+        <v>-5.9172960864</v>
       </c>
       <c r="Q97">
-        <v>-4.882487273000001</v>
+        <v>-4.977296086400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.81877946509903</v>
+        <v>4.762024331373789</v>
       </c>
       <c r="T97">
-        <v>23.07507273024817</v>
+        <v>28.84384091281023</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1025289424033763</v>
+        <v>0.1014609325866745</v>
       </c>
       <c r="W97">
-        <v>0.2116236753812839</v>
+        <v>0.2118755120960622</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3535480772530217</v>
+        <v>0.349865284781636</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3938814648671709</v>
+        <v>0.3957814648671709</v>
       </c>
       <c r="C98">
-        <v>-13.09221582608686</v>
+        <v>-13.78323074476692</v>
       </c>
       <c r="D98">
-        <v>22.97258417391313</v>
+        <v>22.84786925523307</v>
       </c>
       <c r="E98">
-        <v>48.6348</v>
+        <v>49.2011</v>
       </c>
       <c r="F98">
-        <v>54.3648</v>
+        <v>54.93109999999999</v>
       </c>
       <c r="G98">
         <v>18.3</v>
@@ -9323,37 +9323,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M98">
-        <v>12.81921984</v>
+        <v>12.95275338</v>
       </c>
       <c r="N98">
-        <v>-8.334219839999999</v>
+        <v>-8.46775338</v>
       </c>
       <c r="O98">
-        <v>-2.416923753599999</v>
+        <v>-2.4556484802</v>
       </c>
       <c r="P98">
-        <v>-5.9172960864</v>
+        <v>-6.0121048998</v>
       </c>
       <c r="Q98">
-        <v>-4.977296086400001</v>
+        <v>-5.072104899799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.762024331373777</v>
+        <v>6.33409910849837</v>
       </c>
       <c r="T98">
-        <v>28.84384091281015</v>
+        <v>38.45845455041354</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1014609325866745</v>
+        <v>0.1004149435909355</v>
       </c>
       <c r="W98">
-        <v>0.2118755120960622</v>
+        <v>0.2121221563012574</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3498652847816361</v>
+        <v>0.3462584261756398</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3957814648671709</v>
+        <v>0.3976814648671709</v>
       </c>
       <c r="C99">
-        <v>-13.78323074476692</v>
+        <v>-14.47289885567702</v>
       </c>
       <c r="D99">
-        <v>22.84786925523307</v>
+        <v>22.72450114432297</v>
       </c>
       <c r="E99">
-        <v>49.2011</v>
+        <v>49.76739999999999</v>
       </c>
       <c r="F99">
-        <v>54.93109999999999</v>
+        <v>55.49739999999999</v>
       </c>
       <c r="G99">
         <v>18.3</v>
@@ -9405,37 +9405,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M99">
-        <v>12.95275338</v>
+        <v>13.08628692</v>
       </c>
       <c r="N99">
-        <v>-8.46775338</v>
+        <v>-8.60128692</v>
       </c>
       <c r="O99">
-        <v>-2.4556484802</v>
+        <v>-2.4943732068</v>
       </c>
       <c r="P99">
-        <v>-6.0121048998</v>
+        <v>-6.1069137132</v>
       </c>
       <c r="Q99">
-        <v>-5.072104899799999</v>
+        <v>-5.1669137132</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>6.33409910849837</v>
+        <v>9.478248662747552</v>
       </c>
       <c r="T99">
-        <v>38.45845455041354</v>
+        <v>57.6876818256203</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1004149435909355</v>
+        <v>0.0993903013093954</v>
       </c>
       <c r="W99">
-        <v>0.2121221563012574</v>
+        <v>0.2123637669512446</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3462584261756398</v>
+        <v>0.3427251769289497</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3976814648671709</v>
+        <v>0.3995814648671709</v>
       </c>
       <c r="C100">
-        <v>-14.47289885567702</v>
+        <v>-15.16124185810065</v>
       </c>
       <c r="D100">
-        <v>22.72450114432297</v>
+        <v>22.60245814189935</v>
       </c>
       <c r="E100">
-        <v>49.76739999999999</v>
+        <v>50.33369999999999</v>
       </c>
       <c r="F100">
-        <v>55.49739999999999</v>
+        <v>56.0637</v>
       </c>
       <c r="G100">
         <v>18.3</v>
@@ -9487,37 +9487,37 @@
         <v>4.484999999999999</v>
       </c>
       <c r="M100">
-        <v>13.08628692</v>
+        <v>13.21982046</v>
       </c>
       <c r="N100">
-        <v>-8.60128692</v>
+        <v>-8.73482046</v>
       </c>
       <c r="O100">
-        <v>-2.4943732068</v>
+        <v>-2.5330979334</v>
       </c>
       <c r="P100">
-        <v>-6.1069137132</v>
+        <v>-6.2017225266</v>
       </c>
       <c r="Q100">
-        <v>-5.1669137132</v>
+        <v>-5.2617225266</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>9.478248662747552</v>
+        <v>18.91069732549511</v>
       </c>
       <c r="T100">
-        <v>57.6876818256203</v>
+        <v>115.3753636512406</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0993903013093954</v>
+        <v>0.09838635887192676</v>
       </c>
       <c r="W100">
-        <v>0.2123637669512446</v>
+        <v>0.2126004965779997</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3427251769289497</v>
+        <v>0.3392633064549199</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3995814648671709</v>
-      </c>
-      <c r="C101">
-        <v>-15.16124185810065</v>
-      </c>
-      <c r="D101">
-        <v>22.60245814189935</v>
-      </c>
-      <c r="E101">
-        <v>50.33369999999999</v>
-      </c>
-      <c r="F101">
-        <v>56.0637</v>
-      </c>
-      <c r="G101">
-        <v>18.3</v>
-      </c>
-      <c r="H101">
-        <v>50.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.425</v>
-      </c>
-      <c r="K101">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L101">
-        <v>4.484999999999999</v>
-      </c>
-      <c r="M101">
-        <v>13.21982046</v>
-      </c>
-      <c r="N101">
-        <v>-8.73482046</v>
-      </c>
-      <c r="O101">
-        <v>-2.5330979334</v>
-      </c>
-      <c r="P101">
-        <v>-6.2017225266</v>
-      </c>
-      <c r="Q101">
-        <v>-5.2617225266</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>18.91069732549511</v>
-      </c>
-      <c r="T101">
-        <v>115.3753636512406</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09838635887192676</v>
-      </c>
-      <c r="W101">
-        <v>0.2126004965779997</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3392633064549199</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
